--- a/tests/Data/RestdAllState.xlsx
+++ b/tests/Data/RestdAllState.xlsx
@@ -232,7 +232,7 @@
     <t xml:space="preserve">Silver Test</t>
   </si>
   <si>
-    <t xml:space="preserve">123 Connecticut CT usa</t>
+    <t xml:space="preserve">Connecticut CT usa</t>
   </si>
   <si>
     <t xml:space="preserve">52528</t>
@@ -271,7 +271,7 @@
     <t xml:space="preserve">Corn Test</t>
   </si>
   <si>
-    <t xml:space="preserve">123 hawai hi</t>
+    <t xml:space="preserve">Hawaï HI USA</t>
   </si>
   <si>
     <t xml:space="preserve">52532</t>
@@ -481,7 +481,7 @@
     <t xml:space="preserve">Empire Test</t>
   </si>
   <si>
-    <t xml:space="preserve">123 Nevada NV usa</t>
+    <t xml:space="preserve">Medical nv usa</t>
   </si>
   <si>
     <t xml:space="preserve">52554</t>
@@ -508,7 +508,7 @@
     <t xml:space="preserve">Beaver Test</t>
   </si>
   <si>
-    <t xml:space="preserve">123 Oklahoma OK</t>
+    <t xml:space="preserve">123 Oklahoma OK USA</t>
   </si>
   <si>
     <t xml:space="preserve">52557</t>
@@ -643,7 +643,7 @@
     <t xml:space="preserve">Cowboy Test</t>
   </si>
   <si>
-    <t xml:space="preserve">wy usa</t>
+    <t xml:space="preserve">Medical Wy usa</t>
   </si>
   <si>
     <t xml:space="preserve">12</t>

--- a/tests/Data/RestdAllState.xlsx
+++ b/tests/Data/RestdAllState.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1026" uniqueCount="256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1026" uniqueCount="283">
   <si>
     <t xml:space="preserve">State</t>
   </si>
@@ -157,7 +157,7 @@
     <t xml:space="preserve">HHL01-A, Herbert H. Landy</t>
   </si>
   <si>
-    <t xml:space="preserve">NetworkTest</t>
+    <t xml:space="preserve">Reinsurance Company</t>
   </si>
   <si>
     <t xml:space="preserve">Unlimited</t>
@@ -202,7 +202,7 @@
     <t xml:space="preserve">AZ</t>
   </si>
   <si>
-    <t xml:space="preserve">Jenkins Test</t>
+    <t xml:space="preserve">Westchester Fire Insurance Company</t>
   </si>
   <si>
     <t xml:space="preserve">123 Arizona AZ </t>
@@ -214,7 +214,7 @@
     <t xml:space="preserve">AR</t>
   </si>
   <si>
-    <t xml:space="preserve">Board Test</t>
+    <t xml:space="preserve">Everest National Insurance Company</t>
   </si>
   <si>
     <t xml:space="preserve">123 Arkansas AR </t>
@@ -229,7 +229,7 @@
     <t xml:space="preserve">CT</t>
   </si>
   <si>
-    <t xml:space="preserve">Silver Test</t>
+    <t xml:space="preserve">FCCI Insurance Company</t>
   </si>
   <si>
     <t xml:space="preserve">Connecticut CT usa</t>
@@ -244,7 +244,10 @@
     <t xml:space="preserve">DE</t>
   </si>
   <si>
-    <t xml:space="preserve">123 Delaware DE usa</t>
+    <t xml:space="preserve">AMERICAN CONTRACTORS INDEMNITY COMPANY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Delaware DE usa</t>
   </si>
   <si>
     <t xml:space="preserve">52529</t>
@@ -256,541 +259,619 @@
     <t xml:space="preserve">GA</t>
   </si>
   <si>
+    <t xml:space="preserve">Munich Reinsurance America, Inc.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123 Georgia GA usa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52531</t>
+  </si>
+  <si>
     <t xml:space="preserve">Island Test</t>
   </si>
   <si>
-    <t xml:space="preserve">123 Georgia GA usa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52531</t>
-  </si>
-  <si>
     <t xml:space="preserve">HI</t>
   </si>
   <si>
+    <t xml:space="preserve">American Southern Insurance Company</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hawaï HI USA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52532</t>
+  </si>
+  <si>
     <t xml:space="preserve">Corn Test</t>
   </si>
   <si>
-    <t xml:space="preserve">Hawaï HI USA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52532</t>
-  </si>
-  <si>
     <t xml:space="preserve">IA</t>
   </si>
   <si>
+    <t xml:space="preserve">Antilles Insurance Company</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123 Iowa IA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52533</t>
+  </si>
+  <si>
     <t xml:space="preserve">Gem Test</t>
   </si>
   <si>
-    <t xml:space="preserve">123 Iowa IA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52533</t>
-  </si>
-  <si>
     <t xml:space="preserve">ID</t>
   </si>
   <si>
+    <t xml:space="preserve">Arch Reinsurance Company</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123 Idaho ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$ 4,000,000 / $ 4,000,000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52534</t>
+  </si>
+  <si>
     <t xml:space="preserve">Prairie Test</t>
   </si>
   <si>
-    <t xml:space="preserve">123 Idaho ID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">$ 4,000,000 / $ 4,000,000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52534</t>
-  </si>
-  <si>
     <t xml:space="preserve">IL</t>
   </si>
   <si>
+    <t xml:space="preserve">Capitol Indemnity Corporation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123 Illinois IL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52535</t>
+  </si>
+  <si>
     <t xml:space="preserve">Hoosier Test</t>
   </si>
   <si>
-    <t xml:space="preserve">123 Illinois IL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52535</t>
-  </si>
-  <si>
     <t xml:space="preserve">IN</t>
   </si>
   <si>
+    <t xml:space="preserve">CorePointe Insurance Company</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Indiana IN usa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52536</t>
+  </si>
+  <si>
     <t xml:space="preserve">Sunflower Test</t>
   </si>
   <si>
-    <t xml:space="preserve">123 Indiana IN usa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52536</t>
-  </si>
-  <si>
     <t xml:space="preserve">KS</t>
   </si>
   <si>
+    <t xml:space="preserve">Carolina Casualty Insurance Company</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123 Kansas KS usa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52537</t>
+  </si>
+  <si>
     <t xml:space="preserve">Bluegrass Test</t>
   </si>
   <si>
-    <t xml:space="preserve">123 Kansas KS usa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52537</t>
-  </si>
-  <si>
     <t xml:space="preserve">MA</t>
   </si>
   <si>
+    <t xml:space="preserve">Endurance American Insurance Company</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123 Massachusetts MA usa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52540</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bayou Test</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cherokee Insurance Company</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123 Maryland MD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Boston Test</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ME</t>
+  </si>
+  <si>
+    <t xml:space="preserve">United States Surety Company</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maine ME usa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52542</t>
+  </si>
+  <si>
     <t xml:space="preserve">Chesapeake Test</t>
   </si>
   <si>
-    <t xml:space="preserve">123 Massachusetts MA usa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52540</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bayou Test</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MD</t>
+    <t xml:space="preserve">MI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GRAY CASUALTY &amp; SURETY COMPANY (THE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">michigan mi usa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52543</t>
   </si>
   <si>
     <t xml:space="preserve">Pine Test</t>
   </si>
   <si>
-    <t xml:space="preserve">123 Maryland MD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Boston Test</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME</t>
+    <t xml:space="preserve">MO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cincinnati Insurance Company (The)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123 Missouri MO usa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NorthStar Test</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COLONIAL SURETY COMPANY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123 Mississippi MS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ShowMe Test</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CUMIS INSURANCE SOCIETY, INC.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Montana MT usa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$ 1,000,000 / $ 1,000,000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Magnolia Test</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ND</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SureTec Insurance Company</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123 avenue nd usa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TarHeel Test</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seneca Insurance Company, Inc.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123 Nebraska NE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52550</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dakota Test</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">First Net Insurance Company</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123 New Hampshire NH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plains Test</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brierfield Insurance Company</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Medical nv usa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Garden Test</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amerisure Partners Insurance Company</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123 Ohio OH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vegas Test</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arch Insurance Company</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123 Oklahoma OK USA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Empire Test</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Endurance Assurance Corporation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123 Pennsylvania PA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sooner Test</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">International Fidelity Insurance Company</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123 Rhode Island RI usa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52560</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beaver Test</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Merchants National Bonding, Inc.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123 South Carolina SC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keystone Test</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GENERAL STAR NATIONAL INSURANCE COMPANY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123 South Dakota SD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ocean Test</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">General Star National Insurance Company</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123 Tennessee TN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Palmetto Test</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">National Casualty Company</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123 Texas TX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rushmore Test</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">First Founders Assurance Company</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123 Utah UT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Volunteer Test</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123 old Virginia VA usa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LoneStar Test</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123 Washington WA usa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Virginia Test</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123 Wisconsin WI usa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maple Test</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pennsylvania Manufacturers' Association Insurance Company</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Medical Wy usa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$700,001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evergreen Test</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tree Test</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123 northcarolina nc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alignment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123 California CA usa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$800,000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100% CEIL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strong Test</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123 Florida FL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hot Test</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123 Kentucky KY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mountain Test</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123 West Virginia WV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$500,000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NJ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123 New Jersey NJ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">White Test</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123 Colorado CO usa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Badger Test</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123 Minnesota MN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52544</t>
   </si>
   <si>
     <t xml:space="preserve">GreatLake Test</t>
   </si>
   <si>
-    <t xml:space="preserve">Maine ME usa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NorthStar Test</t>
-  </si>
-  <si>
-    <t xml:space="preserve">michigan mi usa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Magnolia Test</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123 Missouri MO usa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BigSky Test</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123 Mississippi MS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ShowMe Test</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TarHeel Test</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Montana MT usa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">$ 1,000,000 / $ 1,000,000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ND</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Plains Test</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123 avenue nd usa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NE</t>
+    <t xml:space="preserve">NM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123 New Mexico NM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$,1000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Loss Only</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52553</t>
   </si>
   <si>
     <t xml:space="preserve">Granite Test</t>
   </si>
   <si>
-    <t xml:space="preserve">123 Nebraska NE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52550</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dakota Test</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Garden Test</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123 New Hampshire NH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NV</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Empire Test</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Medical nv usa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sooner Test</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123 Ohio OH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vegas Test</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beaver Test</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123 Oklahoma OK USA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ocean Test</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123 Pennsylvania PA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Palmetto Test</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123 Rhode Island RI usa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52560</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rushmore Test</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123 South Carolina SC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Keystone Test</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Volunteer Test</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123 South Dakota SD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LoneStar Test</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123 Tennessee TN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TX</t>
+    <t xml:space="preserve">NY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Buckeye Test</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123 New York NY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$ 5,000,000 / $ 5,000,000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$ 100,000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Desert Test</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123 Oregon OR usa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123 Vermont VT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52567</t>
   </si>
   <si>
     <t xml:space="preserve">Beehive Test</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123 Texas TX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Virginia Test</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123 Utah UT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maple Test</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123 Virginia VA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Badger Test</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123 Washington WA usa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mountain Test</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123 Wisconsin WI usa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cowboy Test</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Medical Wy usa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">$700,001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Evergreen Test</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tree Test</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123 northcarolina nc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alignment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123 California CA usa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">$800,000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100% CEIL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strong Test</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123 Florida FL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hot Test</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123 Kentucky KY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WV</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123 West Virginia WV</t>
-  </si>
-  <si>
-    <t xml:space="preserve">$500,000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NJ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123 New Jersey NJ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">White Test</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123 Colorado CO usa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123 Minnesota MN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123 New Mexico NM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">$,1000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Loss Only</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Buckeye Test</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123 New York NY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">$ 5,000,000 / $ 5,000,000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">$ 100,000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Desert Test</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123 Oregon OR usa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123 Vermont VT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52567</t>
   </si>
 </sst>
 </file>
@@ -874,14 +955,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0"/>
-        <bgColor rgb="FFFFF2CC"/>
+        <fgColor theme="9" tint="0.7999"/>
+        <bgColor rgb="FFE7E6E6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.7999"/>
-        <bgColor rgb="FFE7E6E6"/>
+        <fgColor theme="0"/>
+        <bgColor rgb="FFFFF2CC"/>
       </patternFill>
     </fill>
     <fill>
@@ -962,7 +1043,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1003,19 +1084,23 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="8" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="0" fillId="7" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1043,11 +1128,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1325,7 +1410,7 @@
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="3" min="1" style="1" width="8.88"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="26.77"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="15.11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="42.18"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="15.56"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="8" min="7" style="1" width="8.88"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="15.44"/>
@@ -1482,21 +1567,21 @@
       <c r="F2" s="11" t="n">
         <v>46031</v>
       </c>
-      <c r="G2" s="10"/>
-      <c r="H2" s="10"/>
-      <c r="I2" s="12" t="s">
+      <c r="G2" s="12"/>
+      <c r="H2" s="12"/>
+      <c r="I2" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="J2" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="K2" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="L2" s="13"/>
-      <c r="M2" s="13"/>
-      <c r="N2" s="13"/>
-      <c r="O2" s="13"/>
+      <c r="J2" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="K2" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="L2" s="14"/>
+      <c r="M2" s="14"/>
+      <c r="N2" s="14"/>
+      <c r="O2" s="14"/>
       <c r="P2" s="1" t="s">
         <v>47</v>
       </c>
@@ -1506,43 +1591,43 @@
       <c r="T2" s="5"/>
       <c r="U2" s="5"/>
       <c r="V2" s="5"/>
-      <c r="W2" s="14" t="s">
+      <c r="W2" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="X2" s="15"/>
-      <c r="Y2" s="14" t="s">
+      <c r="X2" s="16"/>
+      <c r="Y2" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="Z2" s="15"/>
-      <c r="AA2" s="15"/>
-      <c r="AB2" s="15"/>
-      <c r="AC2" s="15"/>
-      <c r="AD2" s="16" t="s">
+      <c r="Z2" s="16"/>
+      <c r="AA2" s="16"/>
+      <c r="AB2" s="16"/>
+      <c r="AC2" s="16"/>
+      <c r="AD2" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="AE2" s="16" t="s">
+      <c r="AE2" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="AF2" s="17"/>
-      <c r="AG2" s="17"/>
-      <c r="AH2" s="18" t="s">
+      <c r="AF2" s="18"/>
+      <c r="AG2" s="18"/>
+      <c r="AH2" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="AI2" s="18" t="s">
+      <c r="AI2" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="AJ2" s="18" t="s">
+      <c r="AJ2" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="AK2" s="18" t="s">
+      <c r="AK2" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="AL2" s="18"/>
-      <c r="AM2" s="18"/>
-      <c r="AN2" s="19" t="s">
+      <c r="AL2" s="19"/>
+      <c r="AM2" s="19"/>
+      <c r="AN2" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="AU2" s="20" t="s">
+      <c r="AU2" s="21" t="s">
         <v>57</v>
       </c>
     </row>
@@ -1550,28 +1635,28 @@
       <c r="A3" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B3" s="21" t="s">
+      <c r="B3" s="22" t="s">
         <v>41</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D3" s="21" t="s">
+      <c r="D3" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="10" t="s">
         <v>59</v>
       </c>
       <c r="F3" s="11" t="n">
         <v>46031</v>
       </c>
-      <c r="I3" s="12" t="s">
+      <c r="I3" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="J3" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="K3" s="12" t="s">
+      <c r="J3" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="K3" s="13" t="s">
         <v>46</v>
       </c>
       <c r="P3" s="1" t="s">
@@ -1583,43 +1668,43 @@
       <c r="T3" s="8"/>
       <c r="U3" s="8"/>
       <c r="V3" s="8"/>
-      <c r="W3" s="14" t="s">
+      <c r="W3" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="X3" s="14"/>
-      <c r="Y3" s="14" t="s">
+      <c r="X3" s="15"/>
+      <c r="Y3" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="Z3" s="14"/>
-      <c r="AA3" s="14"/>
-      <c r="AB3" s="14"/>
-      <c r="AC3" s="14"/>
-      <c r="AD3" s="16" t="s">
+      <c r="Z3" s="15"/>
+      <c r="AA3" s="15"/>
+      <c r="AB3" s="15"/>
+      <c r="AC3" s="15"/>
+      <c r="AD3" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="AE3" s="16" t="s">
+      <c r="AE3" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="AF3" s="16"/>
-      <c r="AG3" s="16"/>
-      <c r="AH3" s="18" t="s">
+      <c r="AF3" s="17"/>
+      <c r="AG3" s="17"/>
+      <c r="AH3" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="AI3" s="18" t="s">
+      <c r="AI3" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="AJ3" s="18" t="s">
+      <c r="AJ3" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="AK3" s="18" t="s">
+      <c r="AK3" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="AL3" s="18"/>
-      <c r="AM3" s="18"/>
-      <c r="AN3" s="19" t="s">
+      <c r="AL3" s="19"/>
+      <c r="AM3" s="19"/>
+      <c r="AN3" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="AU3" s="20" t="s">
+      <c r="AU3" s="21" t="s">
         <v>61</v>
       </c>
     </row>
@@ -1636,19 +1721,19 @@
       <c r="D4" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="E4" s="21" t="s">
+      <c r="E4" s="10" t="s">
         <v>63</v>
       </c>
       <c r="F4" s="11" t="n">
         <v>46031</v>
       </c>
-      <c r="I4" s="12" t="s">
+      <c r="I4" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="J4" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="K4" s="12" t="s">
+      <c r="J4" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="K4" s="13" t="s">
         <v>46</v>
       </c>
       <c r="P4" s="1" t="s">
@@ -1660,43 +1745,43 @@
       <c r="T4" s="8"/>
       <c r="U4" s="8"/>
       <c r="V4" s="8"/>
-      <c r="W4" s="14" t="s">
+      <c r="W4" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="X4" s="14"/>
-      <c r="Y4" s="14" t="s">
+      <c r="X4" s="15"/>
+      <c r="Y4" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="Z4" s="14"/>
-      <c r="AA4" s="14"/>
-      <c r="AB4" s="14"/>
-      <c r="AC4" s="14"/>
-      <c r="AD4" s="16" t="s">
+      <c r="Z4" s="15"/>
+      <c r="AA4" s="15"/>
+      <c r="AB4" s="15"/>
+      <c r="AC4" s="15"/>
+      <c r="AD4" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="AE4" s="16" t="s">
+      <c r="AE4" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="AF4" s="16"/>
-      <c r="AG4" s="16"/>
-      <c r="AH4" s="18" t="s">
+      <c r="AF4" s="17"/>
+      <c r="AG4" s="17"/>
+      <c r="AH4" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="AI4" s="18" t="s">
+      <c r="AI4" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="AJ4" s="18" t="s">
+      <c r="AJ4" s="19" t="s">
         <v>65</v>
       </c>
-      <c r="AK4" s="18" t="s">
+      <c r="AK4" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="AL4" s="18"/>
-      <c r="AM4" s="18"/>
-      <c r="AN4" s="19" t="s">
+      <c r="AL4" s="19"/>
+      <c r="AM4" s="19"/>
+      <c r="AN4" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="AU4" s="20" t="s">
+      <c r="AU4" s="21" t="s">
         <v>66</v>
       </c>
     </row>
@@ -1704,28 +1789,28 @@
       <c r="A5" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="B5" s="21" t="s">
+      <c r="B5" s="22" t="s">
         <v>41</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D5" s="21" t="s">
+      <c r="D5" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="E5" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="F5" s="22" t="n">
+      <c r="F5" s="23" t="n">
         <v>46027</v>
       </c>
-      <c r="I5" s="12" t="s">
+      <c r="I5" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="J5" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="K5" s="12" t="s">
+      <c r="J5" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="K5" s="13" t="s">
         <v>46</v>
       </c>
       <c r="P5" s="1" t="s">
@@ -1737,43 +1822,43 @@
       <c r="T5" s="8"/>
       <c r="U5" s="8"/>
       <c r="V5" s="8"/>
-      <c r="W5" s="14" t="s">
+      <c r="W5" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="X5" s="14"/>
-      <c r="Y5" s="14" t="s">
+      <c r="X5" s="15"/>
+      <c r="Y5" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="Z5" s="14"/>
-      <c r="AA5" s="14"/>
-      <c r="AB5" s="14"/>
-      <c r="AC5" s="14"/>
-      <c r="AD5" s="16" t="s">
+      <c r="Z5" s="15"/>
+      <c r="AA5" s="15"/>
+      <c r="AB5" s="15"/>
+      <c r="AC5" s="15"/>
+      <c r="AD5" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="AE5" s="16" t="s">
+      <c r="AE5" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="AF5" s="16"/>
-      <c r="AG5" s="16"/>
-      <c r="AH5" s="18" t="s">
+      <c r="AF5" s="17"/>
+      <c r="AG5" s="17"/>
+      <c r="AH5" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="AI5" s="18" t="s">
+      <c r="AI5" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="AJ5" s="18" t="s">
+      <c r="AJ5" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="AK5" s="18" t="s">
+      <c r="AK5" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="AL5" s="18"/>
-      <c r="AM5" s="18"/>
-      <c r="AN5" s="19" t="s">
+      <c r="AL5" s="19"/>
+      <c r="AM5" s="19"/>
+      <c r="AN5" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="AU5" s="20" t="s">
+      <c r="AU5" s="21" t="s">
         <v>71</v>
       </c>
     </row>
@@ -1790,23 +1875,23 @@
       <c r="D6" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="E6" s="21" t="s">
-        <v>71</v>
+      <c r="E6" s="10" t="s">
+        <v>73</v>
       </c>
       <c r="F6" s="11" t="n">
         <v>46027</v>
       </c>
-      <c r="I6" s="12" t="s">
+      <c r="I6" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="J6" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="K6" s="12" t="s">
+      <c r="J6" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="K6" s="13" t="s">
         <v>46</v>
       </c>
       <c r="P6" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="Q6" s="8"/>
       <c r="R6" s="8"/>
@@ -1814,49 +1899,49 @@
       <c r="T6" s="8"/>
       <c r="U6" s="8"/>
       <c r="V6" s="8"/>
-      <c r="W6" s="14" t="s">
+      <c r="W6" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="X6" s="14"/>
-      <c r="Y6" s="14" t="s">
+      <c r="X6" s="15"/>
+      <c r="Y6" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="Z6" s="14"/>
-      <c r="AA6" s="14"/>
-      <c r="AB6" s="14"/>
-      <c r="AC6" s="14"/>
-      <c r="AD6" s="16" t="s">
+      <c r="Z6" s="15"/>
+      <c r="AA6" s="15"/>
+      <c r="AB6" s="15"/>
+      <c r="AC6" s="15"/>
+      <c r="AD6" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="AE6" s="16" t="s">
+      <c r="AE6" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="AF6" s="16"/>
-      <c r="AG6" s="16"/>
-      <c r="AH6" s="18" t="s">
+      <c r="AF6" s="17"/>
+      <c r="AG6" s="17"/>
+      <c r="AH6" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="AI6" s="18" t="s">
+      <c r="AI6" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="AJ6" s="18" t="s">
+      <c r="AJ6" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="AK6" s="18" t="s">
+      <c r="AK6" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="AL6" s="18"/>
-      <c r="AM6" s="18"/>
-      <c r="AN6" s="19" t="s">
-        <v>74</v>
-      </c>
-      <c r="AU6" s="20" t="s">
+      <c r="AL6" s="19"/>
+      <c r="AM6" s="19"/>
+      <c r="AN6" s="20" t="s">
         <v>75</v>
+      </c>
+      <c r="AU6" s="21" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>41</v>
@@ -1867,23 +1952,23 @@
       <c r="D7" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="E7" s="21" t="s">
-        <v>77</v>
+      <c r="E7" s="10" t="s">
+        <v>78</v>
       </c>
       <c r="F7" s="11" t="n">
         <v>46027</v>
       </c>
-      <c r="I7" s="12" t="s">
+      <c r="I7" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="J7" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="K7" s="12" t="s">
+      <c r="J7" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="K7" s="13" t="s">
         <v>46</v>
       </c>
       <c r="P7" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
@@ -1891,76 +1976,76 @@
       <c r="T7" s="8"/>
       <c r="U7" s="8"/>
       <c r="V7" s="8"/>
-      <c r="W7" s="14" t="s">
+      <c r="W7" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="X7" s="14"/>
-      <c r="Y7" s="14" t="s">
+      <c r="X7" s="15"/>
+      <c r="Y7" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="Z7" s="14"/>
-      <c r="AA7" s="14"/>
-      <c r="AB7" s="14"/>
-      <c r="AC7" s="14"/>
-      <c r="AD7" s="16" t="s">
+      <c r="Z7" s="15"/>
+      <c r="AA7" s="15"/>
+      <c r="AB7" s="15"/>
+      <c r="AC7" s="15"/>
+      <c r="AD7" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="AE7" s="16" t="s">
+      <c r="AE7" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="AF7" s="16"/>
-      <c r="AG7" s="16"/>
-      <c r="AH7" s="18" t="s">
+      <c r="AF7" s="17"/>
+      <c r="AG7" s="17"/>
+      <c r="AH7" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="AI7" s="18" t="s">
+      <c r="AI7" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="AJ7" s="18" t="s">
+      <c r="AJ7" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="AK7" s="18" t="s">
+      <c r="AK7" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="AL7" s="18"/>
-      <c r="AM7" s="18"/>
-      <c r="AN7" s="19" t="s">
-        <v>79</v>
-      </c>
-      <c r="AU7" s="20" t="s">
-        <v>77</v>
+      <c r="AL7" s="19"/>
+      <c r="AM7" s="19"/>
+      <c r="AN7" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="AU7" s="21" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="B8" s="21" t="s">
+        <v>82</v>
+      </c>
+      <c r="B8" s="22" t="s">
         <v>41</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D8" s="21" t="s">
+      <c r="D8" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="E8" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="F8" s="22" t="n">
+      <c r="E8" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="F8" s="23" t="n">
         <v>46027</v>
       </c>
-      <c r="I8" s="12" t="s">
+      <c r="I8" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="J8" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="K8" s="12" t="s">
+      <c r="J8" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="K8" s="13" t="s">
         <v>46</v>
       </c>
       <c r="P8" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
@@ -1968,51 +2053,51 @@
       <c r="T8" s="8"/>
       <c r="U8" s="8"/>
       <c r="V8" s="8"/>
-      <c r="W8" s="14" t="s">
+      <c r="W8" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="X8" s="14"/>
-      <c r="Y8" s="14" t="s">
+      <c r="X8" s="15"/>
+      <c r="Y8" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="Z8" s="14"/>
-      <c r="AA8" s="14"/>
-      <c r="AB8" s="14"/>
-      <c r="AC8" s="14"/>
-      <c r="AD8" s="16" t="s">
+      <c r="Z8" s="15"/>
+      <c r="AA8" s="15"/>
+      <c r="AB8" s="15"/>
+      <c r="AC8" s="15"/>
+      <c r="AD8" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="AE8" s="16" t="s">
+      <c r="AE8" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="AF8" s="16"/>
-      <c r="AG8" s="16"/>
-      <c r="AH8" s="18" t="s">
+      <c r="AF8" s="17"/>
+      <c r="AG8" s="17"/>
+      <c r="AH8" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="AI8" s="18" t="s">
+      <c r="AI8" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="AJ8" s="18" t="s">
+      <c r="AJ8" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="AK8" s="18" t="s">
+      <c r="AK8" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="AL8" s="18"/>
-      <c r="AM8" s="18"/>
-      <c r="AN8" s="19" t="s">
-        <v>83</v>
-      </c>
-      <c r="AU8" s="20" t="s">
-        <v>81</v>
+      <c r="AL8" s="19"/>
+      <c r="AM8" s="19"/>
+      <c r="AN8" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="AU8" s="21" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="B9" s="21" t="s">
+        <v>87</v>
+      </c>
+      <c r="B9" s="22" t="s">
         <v>41</v>
       </c>
       <c r="C9" s="1" t="s">
@@ -2021,23 +2106,23 @@
       <c r="D9" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="E9" s="21" t="s">
-        <v>85</v>
+      <c r="E9" s="10" t="s">
+        <v>88</v>
       </c>
       <c r="F9" s="11" t="n">
         <v>46027</v>
       </c>
-      <c r="I9" s="12" t="s">
+      <c r="I9" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="J9" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="K9" s="12" t="s">
+      <c r="J9" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="K9" s="13" t="s">
         <v>46</v>
       </c>
       <c r="P9" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="Q9" s="8"/>
       <c r="R9" s="8"/>
@@ -2045,51 +2130,51 @@
       <c r="T9" s="8"/>
       <c r="U9" s="8"/>
       <c r="V9" s="8"/>
-      <c r="W9" s="14" t="s">
+      <c r="W9" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="X9" s="14"/>
-      <c r="Y9" s="14" t="s">
+      <c r="X9" s="15"/>
+      <c r="Y9" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="Z9" s="14"/>
-      <c r="AA9" s="14"/>
-      <c r="AB9" s="14"/>
-      <c r="AC9" s="14"/>
-      <c r="AD9" s="16" t="s">
+      <c r="Z9" s="15"/>
+      <c r="AA9" s="15"/>
+      <c r="AB9" s="15"/>
+      <c r="AC9" s="15"/>
+      <c r="AD9" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="AE9" s="16" t="s">
+      <c r="AE9" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="AF9" s="16"/>
-      <c r="AG9" s="16"/>
-      <c r="AH9" s="18" t="s">
+      <c r="AF9" s="17"/>
+      <c r="AG9" s="17"/>
+      <c r="AH9" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="AI9" s="18" t="s">
+      <c r="AI9" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="AJ9" s="18" t="s">
+      <c r="AJ9" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="AK9" s="18" t="s">
+      <c r="AK9" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="AL9" s="18"/>
-      <c r="AM9" s="18"/>
-      <c r="AN9" s="19" t="s">
-        <v>87</v>
-      </c>
-      <c r="AU9" s="20" t="s">
-        <v>85</v>
+      <c r="AL9" s="19"/>
+      <c r="AM9" s="19"/>
+      <c r="AN9" s="20" t="s">
+        <v>90</v>
+      </c>
+      <c r="AU9" s="21" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="B10" s="21" t="s">
+        <v>92</v>
+      </c>
+      <c r="B10" s="22" t="s">
         <v>41</v>
       </c>
       <c r="C10" s="1" t="s">
@@ -2098,23 +2183,23 @@
       <c r="D10" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="E10" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="F10" s="22" t="n">
+      <c r="E10" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="F10" s="23" t="n">
         <v>46027</v>
       </c>
-      <c r="I10" s="12" t="s">
+      <c r="I10" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="J10" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="K10" s="12" t="s">
+      <c r="J10" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="K10" s="13" t="s">
         <v>46</v>
       </c>
       <c r="P10" s="1" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="Q10" s="8"/>
       <c r="R10" s="8"/>
@@ -2122,51 +2207,51 @@
       <c r="T10" s="8"/>
       <c r="U10" s="8"/>
       <c r="V10" s="8"/>
-      <c r="W10" s="14" t="s">
+      <c r="W10" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="X10" s="14"/>
-      <c r="Y10" s="14" t="s">
+      <c r="X10" s="15"/>
+      <c r="Y10" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="Z10" s="14"/>
-      <c r="AA10" s="14"/>
-      <c r="AB10" s="14"/>
-      <c r="AC10" s="14"/>
-      <c r="AD10" s="16" t="s">
+      <c r="Z10" s="15"/>
+      <c r="AA10" s="15"/>
+      <c r="AB10" s="15"/>
+      <c r="AC10" s="15"/>
+      <c r="AD10" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="AE10" s="16" t="s">
+      <c r="AE10" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="AF10" s="16"/>
-      <c r="AG10" s="16"/>
-      <c r="AH10" s="18" t="s">
-        <v>91</v>
-      </c>
-      <c r="AI10" s="18" t="s">
+      <c r="AF10" s="17"/>
+      <c r="AG10" s="17"/>
+      <c r="AH10" s="19" t="s">
+        <v>95</v>
+      </c>
+      <c r="AI10" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="AJ10" s="18" t="s">
+      <c r="AJ10" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="AK10" s="18" t="s">
+      <c r="AK10" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="AL10" s="18"/>
-      <c r="AM10" s="18"/>
-      <c r="AN10" s="19" t="s">
-        <v>92</v>
-      </c>
-      <c r="AU10" s="20" t="s">
-        <v>89</v>
+      <c r="AL10" s="19"/>
+      <c r="AM10" s="19"/>
+      <c r="AN10" s="20" t="s">
+        <v>96</v>
+      </c>
+      <c r="AU10" s="21" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="B11" s="21" t="s">
+        <v>98</v>
+      </c>
+      <c r="B11" s="22" t="s">
         <v>41</v>
       </c>
       <c r="C11" s="1" t="s">
@@ -2175,23 +2260,23 @@
       <c r="D11" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="E11" s="21" t="s">
-        <v>94</v>
+      <c r="E11" s="10" t="s">
+        <v>99</v>
       </c>
       <c r="F11" s="11" t="n">
         <v>46027</v>
       </c>
-      <c r="I11" s="12" t="s">
+      <c r="I11" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="J11" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="K11" s="12" t="s">
+      <c r="J11" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="K11" s="13" t="s">
         <v>46</v>
       </c>
       <c r="P11" s="1" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="Q11" s="8"/>
       <c r="R11" s="8"/>
@@ -2199,51 +2284,51 @@
       <c r="T11" s="8"/>
       <c r="U11" s="8"/>
       <c r="V11" s="8"/>
-      <c r="W11" s="14" t="s">
+      <c r="W11" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="X11" s="14"/>
-      <c r="Y11" s="14" t="s">
+      <c r="X11" s="15"/>
+      <c r="Y11" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="Z11" s="14"/>
-      <c r="AA11" s="14"/>
-      <c r="AB11" s="14"/>
-      <c r="AC11" s="14"/>
-      <c r="AD11" s="16" t="s">
+      <c r="Z11" s="15"/>
+      <c r="AA11" s="15"/>
+      <c r="AB11" s="15"/>
+      <c r="AC11" s="15"/>
+      <c r="AD11" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="AE11" s="16" t="s">
+      <c r="AE11" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="AF11" s="16"/>
-      <c r="AG11" s="16"/>
-      <c r="AH11" s="18" t="s">
+      <c r="AF11" s="17"/>
+      <c r="AG11" s="17"/>
+      <c r="AH11" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="AI11" s="18" t="s">
+      <c r="AI11" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="AJ11" s="18" t="s">
+      <c r="AJ11" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="AK11" s="18" t="s">
+      <c r="AK11" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="AL11" s="18"/>
-      <c r="AM11" s="18"/>
-      <c r="AN11" s="19" t="s">
-        <v>96</v>
-      </c>
-      <c r="AU11" s="20" t="s">
-        <v>94</v>
+      <c r="AL11" s="19"/>
+      <c r="AM11" s="19"/>
+      <c r="AN11" s="20" t="s">
+        <v>101</v>
+      </c>
+      <c r="AU11" s="21" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="B12" s="21" t="s">
+        <v>103</v>
+      </c>
+      <c r="B12" s="22" t="s">
         <v>41</v>
       </c>
       <c r="C12" s="1" t="s">
@@ -2252,23 +2337,23 @@
       <c r="D12" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="E12" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="F12" s="22" t="n">
+      <c r="E12" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="F12" s="23" t="n">
         <v>46027</v>
       </c>
-      <c r="I12" s="12" t="s">
+      <c r="I12" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="J12" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="K12" s="12" t="s">
+      <c r="J12" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="K12" s="13" t="s">
         <v>46</v>
       </c>
       <c r="P12" s="1" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="Q12" s="8"/>
       <c r="R12" s="8"/>
@@ -2276,51 +2361,51 @@
       <c r="T12" s="8"/>
       <c r="U12" s="8"/>
       <c r="V12" s="8"/>
-      <c r="W12" s="14" t="s">
+      <c r="W12" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="X12" s="14"/>
-      <c r="Y12" s="14" t="s">
+      <c r="X12" s="15"/>
+      <c r="Y12" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="Z12" s="14"/>
-      <c r="AA12" s="14"/>
-      <c r="AB12" s="14"/>
-      <c r="AC12" s="14"/>
-      <c r="AD12" s="16" t="s">
+      <c r="Z12" s="15"/>
+      <c r="AA12" s="15"/>
+      <c r="AB12" s="15"/>
+      <c r="AC12" s="15"/>
+      <c r="AD12" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="AE12" s="16" t="s">
+      <c r="AE12" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="AF12" s="16"/>
-      <c r="AG12" s="16"/>
-      <c r="AH12" s="18" t="s">
+      <c r="AF12" s="17"/>
+      <c r="AG12" s="17"/>
+      <c r="AH12" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="AI12" s="18" t="s">
+      <c r="AI12" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="AJ12" s="18" t="s">
+      <c r="AJ12" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="AK12" s="18" t="s">
+      <c r="AK12" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="AL12" s="18"/>
-      <c r="AM12" s="18"/>
-      <c r="AN12" s="19" t="s">
-        <v>100</v>
-      </c>
-      <c r="AU12" s="20" t="s">
-        <v>98</v>
+      <c r="AL12" s="19"/>
+      <c r="AM12" s="19"/>
+      <c r="AN12" s="20" t="s">
+        <v>106</v>
+      </c>
+      <c r="AU12" s="21" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="B13" s="21" t="s">
+        <v>108</v>
+      </c>
+      <c r="B13" s="22" t="s">
         <v>41</v>
       </c>
       <c r="C13" s="1" t="s">
@@ -2329,23 +2414,23 @@
       <c r="D13" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="E13" s="21" t="s">
-        <v>102</v>
+      <c r="E13" s="10" t="s">
+        <v>109</v>
       </c>
       <c r="F13" s="11" t="n">
         <v>46027</v>
       </c>
-      <c r="I13" s="12" t="s">
+      <c r="I13" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="J13" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="K13" s="12" t="s">
+      <c r="J13" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="K13" s="13" t="s">
         <v>46</v>
       </c>
       <c r="P13" s="1" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="Q13" s="8"/>
       <c r="R13" s="8"/>
@@ -2353,51 +2438,51 @@
       <c r="T13" s="8"/>
       <c r="U13" s="8"/>
       <c r="V13" s="8"/>
-      <c r="W13" s="14" t="s">
+      <c r="W13" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="X13" s="14"/>
-      <c r="Y13" s="14" t="s">
+      <c r="X13" s="15"/>
+      <c r="Y13" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="Z13" s="14"/>
-      <c r="AA13" s="14"/>
-      <c r="AB13" s="14"/>
-      <c r="AC13" s="14"/>
-      <c r="AD13" s="16" t="s">
+      <c r="Z13" s="15"/>
+      <c r="AA13" s="15"/>
+      <c r="AB13" s="15"/>
+      <c r="AC13" s="15"/>
+      <c r="AD13" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="AE13" s="16" t="s">
+      <c r="AE13" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="AF13" s="16"/>
-      <c r="AG13" s="16"/>
-      <c r="AH13" s="18" t="s">
+      <c r="AF13" s="17"/>
+      <c r="AG13" s="17"/>
+      <c r="AH13" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="AI13" s="18" t="s">
+      <c r="AI13" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="AJ13" s="18" t="s">
+      <c r="AJ13" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="AK13" s="18" t="s">
+      <c r="AK13" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="AL13" s="18"/>
-      <c r="AM13" s="18"/>
-      <c r="AN13" s="19" t="s">
-        <v>104</v>
-      </c>
-      <c r="AU13" s="20" t="s">
-        <v>102</v>
+      <c r="AL13" s="19"/>
+      <c r="AM13" s="19"/>
+      <c r="AN13" s="20" t="s">
+        <v>111</v>
+      </c>
+      <c r="AU13" s="21" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="B14" s="21" t="s">
+        <v>113</v>
+      </c>
+      <c r="B14" s="22" t="s">
         <v>41</v>
       </c>
       <c r="C14" s="1" t="s">
@@ -2406,23 +2491,23 @@
       <c r="D14" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="E14" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="F14" s="22" t="n">
+      <c r="E14" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="F14" s="23" t="n">
         <v>46027</v>
       </c>
-      <c r="I14" s="12" t="s">
+      <c r="I14" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="J14" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="K14" s="12" t="s">
+      <c r="J14" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="K14" s="13" t="s">
         <v>46</v>
       </c>
       <c r="P14" s="1" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="Q14" s="8"/>
       <c r="R14" s="8"/>
@@ -2430,51 +2515,51 @@
       <c r="T14" s="8"/>
       <c r="U14" s="8"/>
       <c r="V14" s="8"/>
-      <c r="W14" s="14" t="s">
+      <c r="W14" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="X14" s="14"/>
-      <c r="Y14" s="14" t="s">
+      <c r="X14" s="15"/>
+      <c r="Y14" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="Z14" s="14"/>
-      <c r="AA14" s="14"/>
-      <c r="AB14" s="14"/>
-      <c r="AC14" s="14"/>
-      <c r="AD14" s="16" t="s">
+      <c r="Z14" s="15"/>
+      <c r="AA14" s="15"/>
+      <c r="AB14" s="15"/>
+      <c r="AC14" s="15"/>
+      <c r="AD14" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="AE14" s="16" t="s">
+      <c r="AE14" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="AF14" s="16"/>
-      <c r="AG14" s="16"/>
-      <c r="AH14" s="18" t="s">
+      <c r="AF14" s="17"/>
+      <c r="AG14" s="17"/>
+      <c r="AH14" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="AI14" s="18" t="s">
+      <c r="AI14" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="AJ14" s="18" t="s">
+      <c r="AJ14" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="AK14" s="18" t="s">
+      <c r="AK14" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="AL14" s="18"/>
-      <c r="AM14" s="18"/>
-      <c r="AN14" s="19" t="s">
-        <v>108</v>
-      </c>
-      <c r="AU14" s="20" t="s">
-        <v>109</v>
+      <c r="AL14" s="19"/>
+      <c r="AM14" s="19"/>
+      <c r="AN14" s="20" t="s">
+        <v>116</v>
+      </c>
+      <c r="AU14" s="21" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="B15" s="21" t="s">
+        <v>118</v>
+      </c>
+      <c r="B15" s="22" t="s">
         <v>41</v>
       </c>
       <c r="C15" s="1" t="s">
@@ -2483,23 +2568,23 @@
       <c r="D15" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="E15" s="21" t="s">
-        <v>111</v>
+      <c r="E15" s="10" t="s">
+        <v>119</v>
       </c>
       <c r="F15" s="11" t="n">
         <v>46027</v>
       </c>
-      <c r="I15" s="12" t="s">
+      <c r="I15" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="J15" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="K15" s="12" t="s">
+      <c r="J15" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="K15" s="13" t="s">
         <v>46</v>
       </c>
       <c r="P15" s="1" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="Q15" s="8"/>
       <c r="R15" s="8"/>
@@ -2507,51 +2592,51 @@
       <c r="T15" s="8"/>
       <c r="U15" s="8"/>
       <c r="V15" s="8"/>
-      <c r="W15" s="14" t="s">
+      <c r="W15" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="X15" s="14"/>
-      <c r="Y15" s="14" t="s">
+      <c r="X15" s="15"/>
+      <c r="Y15" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="Z15" s="14"/>
-      <c r="AA15" s="14"/>
-      <c r="AB15" s="14"/>
-      <c r="AC15" s="14"/>
-      <c r="AD15" s="16" t="s">
+      <c r="Z15" s="15"/>
+      <c r="AA15" s="15"/>
+      <c r="AB15" s="15"/>
+      <c r="AC15" s="15"/>
+      <c r="AD15" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="AE15" s="16" t="s">
+      <c r="AE15" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="AF15" s="16"/>
-      <c r="AG15" s="16"/>
-      <c r="AH15" s="18" t="s">
+      <c r="AF15" s="17"/>
+      <c r="AG15" s="17"/>
+      <c r="AH15" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="AI15" s="18" t="s">
+      <c r="AI15" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="AJ15" s="18" t="s">
+      <c r="AJ15" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="AK15" s="18" t="s">
+      <c r="AK15" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="AL15" s="18"/>
-      <c r="AM15" s="18"/>
-      <c r="AN15" s="19" t="s">
-        <v>113</v>
-      </c>
-      <c r="AU15" s="20" t="s">
-        <v>114</v>
+      <c r="AL15" s="19"/>
+      <c r="AM15" s="19"/>
+      <c r="AN15" s="20" t="s">
+        <v>121</v>
+      </c>
+      <c r="AU15" s="21" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="B16" s="21" t="s">
+        <v>123</v>
+      </c>
+      <c r="B16" s="22" t="s">
         <v>41</v>
       </c>
       <c r="C16" s="1" t="s">
@@ -2560,23 +2645,23 @@
       <c r="D16" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="E16" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="F16" s="22" t="n">
+      <c r="E16" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="F16" s="23" t="n">
         <v>46027</v>
       </c>
-      <c r="I16" s="12" t="s">
+      <c r="I16" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="J16" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="K16" s="12" t="s">
+      <c r="J16" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="K16" s="13" t="s">
         <v>46</v>
       </c>
       <c r="P16" s="1" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="Q16" s="8"/>
       <c r="R16" s="8"/>
@@ -2584,51 +2669,51 @@
       <c r="T16" s="8"/>
       <c r="U16" s="8"/>
       <c r="V16" s="8"/>
-      <c r="W16" s="14" t="s">
+      <c r="W16" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="X16" s="14"/>
-      <c r="Y16" s="14" t="s">
+      <c r="X16" s="15"/>
+      <c r="Y16" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="Z16" s="14"/>
-      <c r="AA16" s="14"/>
-      <c r="AB16" s="14"/>
-      <c r="AC16" s="14"/>
-      <c r="AD16" s="16" t="s">
+      <c r="Z16" s="15"/>
+      <c r="AA16" s="15"/>
+      <c r="AB16" s="15"/>
+      <c r="AC16" s="15"/>
+      <c r="AD16" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="AE16" s="16" t="s">
+      <c r="AE16" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="AF16" s="16"/>
-      <c r="AG16" s="16"/>
-      <c r="AH16" s="18" t="s">
-        <v>91</v>
-      </c>
-      <c r="AI16" s="18" t="s">
+      <c r="AF16" s="17"/>
+      <c r="AG16" s="17"/>
+      <c r="AH16" s="19" t="s">
+        <v>95</v>
+      </c>
+      <c r="AI16" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="AJ16" s="18" t="s">
+      <c r="AJ16" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="AK16" s="18" t="s">
+      <c r="AK16" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="AL16" s="18"/>
-      <c r="AM16" s="18"/>
-      <c r="AN16" s="19" t="s">
-        <v>118</v>
-      </c>
-      <c r="AU16" s="20" t="s">
-        <v>106</v>
+      <c r="AL16" s="19"/>
+      <c r="AM16" s="19"/>
+      <c r="AN16" s="20" t="s">
+        <v>126</v>
+      </c>
+      <c r="AU16" s="21" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="B17" s="21" t="s">
+        <v>128</v>
+      </c>
+      <c r="B17" s="22" t="s">
         <v>41</v>
       </c>
       <c r="C17" s="1" t="s">
@@ -2637,23 +2722,23 @@
       <c r="D17" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="E17" s="21" t="s">
-        <v>120</v>
+      <c r="E17" s="10" t="s">
+        <v>129</v>
       </c>
       <c r="F17" s="11" t="n">
         <v>46027</v>
       </c>
-      <c r="I17" s="12" t="s">
+      <c r="I17" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="J17" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="K17" s="12" t="s">
+      <c r="J17" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="K17" s="13" t="s">
         <v>46</v>
       </c>
       <c r="P17" s="1" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="Q17" s="8"/>
       <c r="R17" s="8"/>
@@ -2661,51 +2746,51 @@
       <c r="T17" s="8"/>
       <c r="U17" s="8"/>
       <c r="V17" s="8"/>
-      <c r="W17" s="14" t="s">
+      <c r="W17" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="X17" s="14"/>
-      <c r="Y17" s="14" t="s">
+      <c r="X17" s="15"/>
+      <c r="Y17" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="Z17" s="14"/>
-      <c r="AA17" s="14"/>
-      <c r="AB17" s="14"/>
-      <c r="AC17" s="14"/>
-      <c r="AD17" s="16" t="s">
+      <c r="Z17" s="15"/>
+      <c r="AA17" s="15"/>
+      <c r="AB17" s="15"/>
+      <c r="AC17" s="15"/>
+      <c r="AD17" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="AE17" s="16" t="s">
+      <c r="AE17" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="AF17" s="16"/>
-      <c r="AG17" s="16"/>
-      <c r="AH17" s="18" t="s">
+      <c r="AF17" s="17"/>
+      <c r="AG17" s="17"/>
+      <c r="AH17" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="AI17" s="18" t="s">
+      <c r="AI17" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="AJ17" s="18" t="s">
+      <c r="AJ17" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="AK17" s="18" t="s">
+      <c r="AK17" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="AL17" s="18"/>
-      <c r="AM17" s="18"/>
-      <c r="AN17" s="19" t="s">
-        <v>122</v>
-      </c>
-      <c r="AU17" s="20" t="s">
-        <v>111</v>
+      <c r="AL17" s="19"/>
+      <c r="AM17" s="19"/>
+      <c r="AN17" s="20" t="s">
+        <v>131</v>
+      </c>
+      <c r="AU17" s="21" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="B18" s="21" t="s">
+        <v>133</v>
+      </c>
+      <c r="B18" s="22" t="s">
         <v>41</v>
       </c>
       <c r="C18" s="1" t="s">
@@ -2714,23 +2799,23 @@
       <c r="D18" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="E18" s="21" t="s">
-        <v>124</v>
+      <c r="E18" s="10" t="s">
+        <v>134</v>
       </c>
       <c r="F18" s="11" t="n">
         <v>46027</v>
       </c>
-      <c r="I18" s="12" t="s">
+      <c r="I18" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="J18" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="K18" s="12" t="s">
+      <c r="J18" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="K18" s="13" t="s">
         <v>46</v>
       </c>
       <c r="P18" s="1" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="Q18" s="8"/>
       <c r="R18" s="8"/>
@@ -2738,51 +2823,51 @@
       <c r="T18" s="8"/>
       <c r="U18" s="8"/>
       <c r="V18" s="8"/>
-      <c r="W18" s="14" t="s">
+      <c r="W18" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="X18" s="14"/>
-      <c r="Y18" s="14" t="s">
+      <c r="X18" s="15"/>
+      <c r="Y18" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="Z18" s="14"/>
-      <c r="AA18" s="14"/>
-      <c r="AB18" s="14"/>
-      <c r="AC18" s="14"/>
-      <c r="AD18" s="16" t="s">
+      <c r="Z18" s="15"/>
+      <c r="AA18" s="15"/>
+      <c r="AB18" s="15"/>
+      <c r="AC18" s="15"/>
+      <c r="AD18" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="AE18" s="16" t="s">
+      <c r="AE18" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="AF18" s="16"/>
-      <c r="AG18" s="16"/>
-      <c r="AH18" s="18" t="s">
+      <c r="AF18" s="17"/>
+      <c r="AG18" s="17"/>
+      <c r="AH18" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="AI18" s="18" t="s">
+      <c r="AI18" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="AJ18" s="18" t="s">
+      <c r="AJ18" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="AK18" s="18" t="s">
+      <c r="AK18" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="AL18" s="18"/>
-      <c r="AM18" s="18"/>
-      <c r="AN18" s="19" t="s">
-        <v>126</v>
-      </c>
-      <c r="AU18" s="20" t="s">
-        <v>120</v>
+      <c r="AL18" s="19"/>
+      <c r="AM18" s="19"/>
+      <c r="AN18" s="20" t="s">
+        <v>136</v>
+      </c>
+      <c r="AU18" s="21" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="B19" s="21" t="s">
+        <v>138</v>
+      </c>
+      <c r="B19" s="22" t="s">
         <v>41</v>
       </c>
       <c r="C19" s="1" t="s">
@@ -2791,23 +2876,23 @@
       <c r="D19" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="E19" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="F19" s="22" t="n">
+      <c r="E19" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="F19" s="23" t="n">
         <v>46027</v>
       </c>
-      <c r="I19" s="12" t="s">
+      <c r="I19" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="J19" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="K19" s="12" t="s">
+      <c r="J19" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="K19" s="13" t="s">
         <v>46</v>
       </c>
       <c r="P19" s="1" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="Q19" s="8"/>
       <c r="R19" s="8"/>
@@ -2815,51 +2900,51 @@
       <c r="T19" s="8"/>
       <c r="U19" s="8"/>
       <c r="V19" s="8"/>
-      <c r="W19" s="14" t="s">
+      <c r="W19" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="X19" s="14"/>
-      <c r="Y19" s="14" t="s">
+      <c r="X19" s="15"/>
+      <c r="Y19" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="Z19" s="14"/>
-      <c r="AA19" s="14"/>
-      <c r="AB19" s="14"/>
-      <c r="AC19" s="14"/>
-      <c r="AD19" s="16" t="s">
+      <c r="Z19" s="15"/>
+      <c r="AA19" s="15"/>
+      <c r="AB19" s="15"/>
+      <c r="AC19" s="15"/>
+      <c r="AD19" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="AE19" s="16" t="s">
+      <c r="AE19" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="AF19" s="16"/>
-      <c r="AG19" s="16"/>
-      <c r="AH19" s="18" t="s">
-        <v>91</v>
-      </c>
-      <c r="AI19" s="18" t="s">
+      <c r="AF19" s="17"/>
+      <c r="AG19" s="17"/>
+      <c r="AH19" s="19" t="s">
+        <v>95</v>
+      </c>
+      <c r="AI19" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="AJ19" s="18" t="s">
+      <c r="AJ19" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="AK19" s="18" t="s">
+      <c r="AK19" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="AL19" s="18"/>
-      <c r="AM19" s="18"/>
-      <c r="AN19" s="19" t="s">
-        <v>130</v>
-      </c>
-      <c r="AU19" s="20" t="s">
-        <v>131</v>
+      <c r="AL19" s="19"/>
+      <c r="AM19" s="19"/>
+      <c r="AN19" s="20" t="s">
+        <v>141</v>
+      </c>
+      <c r="AU19" s="21" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="B20" s="21" t="s">
+        <v>143</v>
+      </c>
+      <c r="B20" s="22" t="s">
         <v>41</v>
       </c>
       <c r="C20" s="1" t="s">
@@ -2868,23 +2953,23 @@
       <c r="D20" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="E20" s="21" t="s">
-        <v>133</v>
+      <c r="E20" s="10" t="s">
+        <v>144</v>
       </c>
       <c r="F20" s="11" t="n">
         <v>46027</v>
       </c>
-      <c r="I20" s="12" t="s">
+      <c r="I20" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="J20" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="K20" s="12" t="s">
+      <c r="J20" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="K20" s="13" t="s">
         <v>46</v>
       </c>
       <c r="P20" s="1" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="Q20" s="8"/>
       <c r="R20" s="8"/>
@@ -2892,51 +2977,51 @@
       <c r="T20" s="8"/>
       <c r="U20" s="8"/>
       <c r="V20" s="8"/>
-      <c r="W20" s="14" t="s">
+      <c r="W20" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="X20" s="14"/>
-      <c r="Y20" s="14" t="s">
+      <c r="X20" s="15"/>
+      <c r="Y20" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="Z20" s="14"/>
-      <c r="AA20" s="14"/>
-      <c r="AB20" s="14"/>
-      <c r="AC20" s="14"/>
-      <c r="AD20" s="16" t="s">
+      <c r="Z20" s="15"/>
+      <c r="AA20" s="15"/>
+      <c r="AB20" s="15"/>
+      <c r="AC20" s="15"/>
+      <c r="AD20" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="AE20" s="16" t="s">
+      <c r="AE20" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="AF20" s="16"/>
-      <c r="AG20" s="16"/>
-      <c r="AH20" s="18" t="s">
-        <v>135</v>
-      </c>
-      <c r="AI20" s="18" t="s">
+      <c r="AF20" s="17"/>
+      <c r="AG20" s="17"/>
+      <c r="AH20" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="AI20" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="AJ20" s="18" t="s">
+      <c r="AJ20" s="19" t="s">
         <v>65</v>
       </c>
-      <c r="AK20" s="18" t="s">
+      <c r="AK20" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="AL20" s="18"/>
-      <c r="AM20" s="18"/>
-      <c r="AN20" s="19" t="s">
-        <v>136</v>
-      </c>
-      <c r="AU20" s="20" t="s">
-        <v>124</v>
+      <c r="AL20" s="19"/>
+      <c r="AM20" s="19"/>
+      <c r="AN20" s="20" t="s">
+        <v>147</v>
+      </c>
+      <c r="AU20" s="21" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="B21" s="21" t="s">
+        <v>149</v>
+      </c>
+      <c r="B21" s="22" t="s">
         <v>41</v>
       </c>
       <c r="C21" s="1" t="s">
@@ -2945,23 +3030,23 @@
       <c r="D21" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="E21" s="21" t="s">
-        <v>138</v>
+      <c r="E21" s="10" t="s">
+        <v>150</v>
       </c>
       <c r="F21" s="11" t="n">
         <v>46027</v>
       </c>
-      <c r="I21" s="12" t="s">
+      <c r="I21" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="J21" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="K21" s="12" t="s">
+      <c r="J21" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="K21" s="13" t="s">
         <v>46</v>
       </c>
       <c r="P21" s="1" t="s">
-        <v>139</v>
+        <v>151</v>
       </c>
       <c r="Q21" s="8"/>
       <c r="R21" s="8"/>
@@ -2969,51 +3054,51 @@
       <c r="T21" s="8"/>
       <c r="U21" s="8"/>
       <c r="V21" s="8"/>
-      <c r="W21" s="14" t="s">
+      <c r="W21" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="X21" s="14"/>
-      <c r="Y21" s="14" t="s">
+      <c r="X21" s="15"/>
+      <c r="Y21" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="Z21" s="14"/>
-      <c r="AA21" s="14"/>
-      <c r="AB21" s="14"/>
-      <c r="AC21" s="14"/>
-      <c r="AD21" s="16" t="s">
+      <c r="Z21" s="15"/>
+      <c r="AA21" s="15"/>
+      <c r="AB21" s="15"/>
+      <c r="AC21" s="15"/>
+      <c r="AD21" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="AE21" s="16" t="s">
+      <c r="AE21" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="AF21" s="16"/>
-      <c r="AG21" s="16"/>
-      <c r="AH21" s="18" t="s">
-        <v>135</v>
-      </c>
-      <c r="AI21" s="18" t="s">
+      <c r="AF21" s="17"/>
+      <c r="AG21" s="17"/>
+      <c r="AH21" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="AI21" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="AJ21" s="18" t="s">
+      <c r="AJ21" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="AK21" s="18" t="s">
+      <c r="AK21" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="AL21" s="18"/>
-      <c r="AM21" s="18"/>
-      <c r="AN21" s="19" t="s">
-        <v>140</v>
-      </c>
-      <c r="AU21" s="20" t="s">
-        <v>133</v>
+      <c r="AL21" s="19"/>
+      <c r="AM21" s="19"/>
+      <c r="AN21" s="20" t="s">
+        <v>152</v>
+      </c>
+      <c r="AU21" s="21" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="B22" s="21" t="s">
+        <v>154</v>
+      </c>
+      <c r="B22" s="22" t="s">
         <v>41</v>
       </c>
       <c r="C22" s="1" t="s">
@@ -3022,23 +3107,23 @@
       <c r="D22" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="E22" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="F22" s="22" t="n">
+      <c r="E22" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="F22" s="23" t="n">
         <v>46027</v>
       </c>
-      <c r="I22" s="12" t="s">
+      <c r="I22" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="J22" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="K22" s="12" t="s">
+      <c r="J22" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="K22" s="13" t="s">
         <v>46</v>
       </c>
       <c r="P22" s="1" t="s">
-        <v>143</v>
+        <v>156</v>
       </c>
       <c r="Q22" s="8"/>
       <c r="R22" s="8"/>
@@ -3046,51 +3131,51 @@
       <c r="T22" s="8"/>
       <c r="U22" s="8"/>
       <c r="V22" s="8"/>
-      <c r="W22" s="14" t="s">
+      <c r="W22" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="X22" s="14"/>
-      <c r="Y22" s="14" t="s">
+      <c r="X22" s="15"/>
+      <c r="Y22" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="Z22" s="14"/>
-      <c r="AA22" s="14"/>
-      <c r="AB22" s="14"/>
-      <c r="AC22" s="14"/>
-      <c r="AD22" s="16" t="s">
+      <c r="Z22" s="15"/>
+      <c r="AA22" s="15"/>
+      <c r="AB22" s="15"/>
+      <c r="AC22" s="15"/>
+      <c r="AD22" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="AE22" s="16" t="s">
+      <c r="AE22" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="AF22" s="16"/>
-      <c r="AG22" s="16"/>
-      <c r="AH22" s="18" t="s">
-        <v>91</v>
-      </c>
-      <c r="AI22" s="18" t="s">
+      <c r="AF22" s="17"/>
+      <c r="AG22" s="17"/>
+      <c r="AH22" s="19" t="s">
+        <v>95</v>
+      </c>
+      <c r="AI22" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="AJ22" s="18" t="s">
+      <c r="AJ22" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="AK22" s="18" t="s">
+      <c r="AK22" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="AL22" s="18"/>
-      <c r="AM22" s="18"/>
-      <c r="AN22" s="19" t="s">
-        <v>144</v>
-      </c>
-      <c r="AU22" s="20" t="s">
-        <v>145</v>
+      <c r="AL22" s="19"/>
+      <c r="AM22" s="19"/>
+      <c r="AN22" s="20" t="s">
+        <v>157</v>
+      </c>
+      <c r="AU22" s="21" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="B23" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="B23" s="22" t="s">
         <v>41</v>
       </c>
       <c r="C23" s="1" t="s">
@@ -3099,23 +3184,23 @@
       <c r="D23" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="E23" s="21" t="s">
-        <v>147</v>
+      <c r="E23" s="10" t="s">
+        <v>160</v>
       </c>
       <c r="F23" s="11" t="n">
         <v>46027</v>
       </c>
-      <c r="I23" s="12" t="s">
+      <c r="I23" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="J23" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="K23" s="12" t="s">
+      <c r="J23" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="K23" s="13" t="s">
         <v>46</v>
       </c>
       <c r="P23" s="1" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
       <c r="Q23" s="8"/>
       <c r="R23" s="8"/>
@@ -3123,51 +3208,51 @@
       <c r="T23" s="8"/>
       <c r="U23" s="8"/>
       <c r="V23" s="8"/>
-      <c r="W23" s="14" t="s">
+      <c r="W23" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="X23" s="14"/>
-      <c r="Y23" s="14" t="s">
+      <c r="X23" s="15"/>
+      <c r="Y23" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="Z23" s="14"/>
-      <c r="AA23" s="14"/>
-      <c r="AB23" s="14"/>
-      <c r="AC23" s="14"/>
-      <c r="AD23" s="16" t="s">
+      <c r="Z23" s="15"/>
+      <c r="AA23" s="15"/>
+      <c r="AB23" s="15"/>
+      <c r="AC23" s="15"/>
+      <c r="AD23" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="AE23" s="16" t="s">
+      <c r="AE23" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="AF23" s="16"/>
-      <c r="AG23" s="16"/>
-      <c r="AH23" s="18" t="s">
+      <c r="AF23" s="17"/>
+      <c r="AG23" s="17"/>
+      <c r="AH23" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="AI23" s="18" t="s">
+      <c r="AI23" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="AJ23" s="18" t="s">
+      <c r="AJ23" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="AK23" s="18" t="s">
+      <c r="AK23" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="AL23" s="18"/>
-      <c r="AM23" s="18"/>
-      <c r="AN23" s="19" t="s">
-        <v>149</v>
-      </c>
-      <c r="AU23" s="20" t="s">
-        <v>138</v>
+      <c r="AL23" s="19"/>
+      <c r="AM23" s="19"/>
+      <c r="AN23" s="20" t="s">
+        <v>162</v>
+      </c>
+      <c r="AU23" s="21" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="B24" s="21" t="s">
+        <v>164</v>
+      </c>
+      <c r="B24" s="22" t="s">
         <v>41</v>
       </c>
       <c r="C24" s="1" t="s">
@@ -3176,23 +3261,23 @@
       <c r="D24" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="E24" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="F24" s="22" t="n">
+      <c r="E24" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="F24" s="23" t="n">
         <v>46027</v>
       </c>
-      <c r="I24" s="12" t="s">
+      <c r="I24" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="J24" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="K24" s="12" t="s">
+      <c r="J24" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="K24" s="13" t="s">
         <v>46</v>
       </c>
       <c r="P24" s="1" t="s">
-        <v>152</v>
+        <v>166</v>
       </c>
       <c r="Q24" s="8"/>
       <c r="R24" s="8"/>
@@ -3200,51 +3285,51 @@
       <c r="T24" s="8"/>
       <c r="U24" s="8"/>
       <c r="V24" s="8"/>
-      <c r="W24" s="14" t="s">
+      <c r="W24" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="X24" s="14"/>
-      <c r="Y24" s="14" t="s">
+      <c r="X24" s="15"/>
+      <c r="Y24" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="Z24" s="14"/>
-      <c r="AA24" s="14"/>
-      <c r="AB24" s="14"/>
-      <c r="AC24" s="14"/>
-      <c r="AD24" s="16" t="s">
+      <c r="Z24" s="15"/>
+      <c r="AA24" s="15"/>
+      <c r="AB24" s="15"/>
+      <c r="AC24" s="15"/>
+      <c r="AD24" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="AE24" s="16" t="s">
+      <c r="AE24" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="AF24" s="16"/>
-      <c r="AG24" s="16"/>
-      <c r="AH24" s="18" t="s">
-        <v>91</v>
-      </c>
-      <c r="AI24" s="18" t="s">
+      <c r="AF24" s="17"/>
+      <c r="AG24" s="17"/>
+      <c r="AH24" s="19" t="s">
+        <v>95</v>
+      </c>
+      <c r="AI24" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="AJ24" s="18" t="s">
+      <c r="AJ24" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="AK24" s="18" t="s">
+      <c r="AK24" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="AL24" s="18"/>
-      <c r="AM24" s="18"/>
-      <c r="AN24" s="19" t="s">
-        <v>153</v>
-      </c>
-      <c r="AU24" s="20" t="s">
-        <v>147</v>
+      <c r="AL24" s="19"/>
+      <c r="AM24" s="19"/>
+      <c r="AN24" s="20" t="s">
+        <v>167</v>
+      </c>
+      <c r="AU24" s="21" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="B25" s="21" t="s">
+        <v>169</v>
+      </c>
+      <c r="B25" s="22" t="s">
         <v>41</v>
       </c>
       <c r="C25" s="1" t="s">
@@ -3253,23 +3338,23 @@
       <c r="D25" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="E25" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="F25" s="22" t="n">
+      <c r="E25" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="F25" s="23" t="n">
         <v>46027</v>
       </c>
-      <c r="I25" s="12" t="s">
+      <c r="I25" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="J25" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="K25" s="12" t="s">
+      <c r="J25" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="K25" s="13" t="s">
         <v>46</v>
       </c>
       <c r="P25" s="1" t="s">
-        <v>156</v>
+        <v>171</v>
       </c>
       <c r="Q25" s="8"/>
       <c r="R25" s="8"/>
@@ -3277,51 +3362,51 @@
       <c r="T25" s="8"/>
       <c r="U25" s="8"/>
       <c r="V25" s="8"/>
-      <c r="W25" s="14" t="s">
+      <c r="W25" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="X25" s="14"/>
-      <c r="Y25" s="14" t="s">
+      <c r="X25" s="15"/>
+      <c r="Y25" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="Z25" s="14"/>
-      <c r="AA25" s="14"/>
-      <c r="AB25" s="14"/>
-      <c r="AC25" s="14"/>
-      <c r="AD25" s="16" t="s">
+      <c r="Z25" s="15"/>
+      <c r="AA25" s="15"/>
+      <c r="AB25" s="15"/>
+      <c r="AC25" s="15"/>
+      <c r="AD25" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="AE25" s="16" t="s">
+      <c r="AE25" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="AF25" s="16"/>
-      <c r="AG25" s="16"/>
-      <c r="AH25" s="18" t="s">
+      <c r="AF25" s="17"/>
+      <c r="AG25" s="17"/>
+      <c r="AH25" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="AI25" s="18" t="s">
+      <c r="AI25" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="AJ25" s="18" t="s">
+      <c r="AJ25" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="AK25" s="18" t="s">
+      <c r="AK25" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="AL25" s="18"/>
-      <c r="AM25" s="18"/>
-      <c r="AN25" s="19" t="s">
-        <v>157</v>
-      </c>
-      <c r="AU25" s="20" t="s">
-        <v>158</v>
+      <c r="AL25" s="19"/>
+      <c r="AM25" s="19"/>
+      <c r="AN25" s="20" t="s">
+        <v>172</v>
+      </c>
+      <c r="AU25" s="21" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="B26" s="21" t="s">
+        <v>174</v>
+      </c>
+      <c r="B26" s="22" t="s">
         <v>41</v>
       </c>
       <c r="C26" s="1" t="s">
@@ -3330,23 +3415,23 @@
       <c r="D26" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="E26" s="21" t="s">
-        <v>160</v>
+      <c r="E26" s="10" t="s">
+        <v>175</v>
       </c>
       <c r="F26" s="11" t="n">
         <v>46027</v>
       </c>
-      <c r="I26" s="12" t="s">
+      <c r="I26" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="J26" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="K26" s="12" t="s">
+      <c r="J26" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="K26" s="13" t="s">
         <v>46</v>
       </c>
       <c r="P26" s="1" t="s">
-        <v>161</v>
+        <v>176</v>
       </c>
       <c r="Q26" s="8"/>
       <c r="R26" s="8"/>
@@ -3354,51 +3439,51 @@
       <c r="T26" s="8"/>
       <c r="U26" s="8"/>
       <c r="V26" s="8"/>
-      <c r="W26" s="14" t="s">
+      <c r="W26" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="X26" s="14"/>
-      <c r="Y26" s="14" t="s">
+      <c r="X26" s="15"/>
+      <c r="Y26" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="Z26" s="14"/>
-      <c r="AA26" s="14"/>
-      <c r="AB26" s="14"/>
-      <c r="AC26" s="14"/>
-      <c r="AD26" s="16" t="s">
+      <c r="Z26" s="15"/>
+      <c r="AA26" s="15"/>
+      <c r="AB26" s="15"/>
+      <c r="AC26" s="15"/>
+      <c r="AD26" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="AE26" s="16" t="s">
+      <c r="AE26" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="AF26" s="16"/>
-      <c r="AG26" s="16"/>
-      <c r="AH26" s="18" t="s">
+      <c r="AF26" s="17"/>
+      <c r="AG26" s="17"/>
+      <c r="AH26" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="AI26" s="18" t="s">
+      <c r="AI26" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="AJ26" s="18" t="s">
+      <c r="AJ26" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="AK26" s="18" t="s">
+      <c r="AK26" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="AL26" s="18"/>
-      <c r="AM26" s="18"/>
-      <c r="AN26" s="19" t="s">
-        <v>162</v>
-      </c>
-      <c r="AU26" s="20" t="s">
-        <v>151</v>
+      <c r="AL26" s="19"/>
+      <c r="AM26" s="19"/>
+      <c r="AN26" s="20" t="s">
+        <v>177</v>
+      </c>
+      <c r="AU26" s="21" t="s">
+        <v>178</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="B27" s="21" t="s">
+        <v>179</v>
+      </c>
+      <c r="B27" s="22" t="s">
         <v>41</v>
       </c>
       <c r="C27" s="1" t="s">
@@ -3407,23 +3492,23 @@
       <c r="D27" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="E27" s="21" t="s">
-        <v>164</v>
+      <c r="E27" s="10" t="s">
+        <v>180</v>
       </c>
       <c r="F27" s="11" t="n">
         <v>46027</v>
       </c>
-      <c r="I27" s="12" t="s">
+      <c r="I27" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="J27" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="K27" s="12" t="s">
+      <c r="J27" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="K27" s="13" t="s">
         <v>46</v>
       </c>
       <c r="P27" s="1" t="s">
-        <v>165</v>
+        <v>181</v>
       </c>
       <c r="Q27" s="8"/>
       <c r="R27" s="8"/>
@@ -3431,51 +3516,51 @@
       <c r="T27" s="8"/>
       <c r="U27" s="8"/>
       <c r="V27" s="8"/>
-      <c r="W27" s="14" t="s">
+      <c r="W27" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="X27" s="14"/>
-      <c r="Y27" s="14" t="s">
+      <c r="X27" s="15"/>
+      <c r="Y27" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="Z27" s="14"/>
-      <c r="AA27" s="14"/>
-      <c r="AB27" s="14"/>
-      <c r="AC27" s="14"/>
-      <c r="AD27" s="16" t="s">
+      <c r="Z27" s="15"/>
+      <c r="AA27" s="15"/>
+      <c r="AB27" s="15"/>
+      <c r="AC27" s="15"/>
+      <c r="AD27" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="AE27" s="16" t="s">
+      <c r="AE27" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="AF27" s="16"/>
-      <c r="AG27" s="16"/>
-      <c r="AH27" s="18" t="s">
+      <c r="AF27" s="17"/>
+      <c r="AG27" s="17"/>
+      <c r="AH27" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="AI27" s="18" t="s">
+      <c r="AI27" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="AJ27" s="18" t="s">
+      <c r="AJ27" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="AK27" s="18" t="s">
+      <c r="AK27" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="AL27" s="18"/>
-      <c r="AM27" s="18"/>
-      <c r="AN27" s="19" t="s">
-        <v>166</v>
-      </c>
-      <c r="AU27" s="20" t="s">
-        <v>155</v>
+      <c r="AL27" s="19"/>
+      <c r="AM27" s="19"/>
+      <c r="AN27" s="20" t="s">
+        <v>182</v>
+      </c>
+      <c r="AU27" s="21" t="s">
+        <v>183</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="B28" s="21" t="s">
+        <v>184</v>
+      </c>
+      <c r="B28" s="22" t="s">
         <v>41</v>
       </c>
       <c r="C28" s="1" t="s">
@@ -3484,23 +3569,23 @@
       <c r="D28" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="E28" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="F28" s="22" t="n">
+      <c r="E28" s="10" t="s">
+        <v>185</v>
+      </c>
+      <c r="F28" s="23" t="n">
         <v>46027</v>
       </c>
-      <c r="I28" s="12" t="s">
+      <c r="I28" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="J28" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="K28" s="12" t="s">
+      <c r="J28" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="K28" s="13" t="s">
         <v>46</v>
       </c>
       <c r="P28" s="1" t="s">
-        <v>169</v>
+        <v>186</v>
       </c>
       <c r="Q28" s="8"/>
       <c r="R28" s="8"/>
@@ -3508,51 +3593,51 @@
       <c r="T28" s="8"/>
       <c r="U28" s="8"/>
       <c r="V28" s="8"/>
-      <c r="W28" s="14" t="s">
+      <c r="W28" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="X28" s="14"/>
-      <c r="Y28" s="14" t="s">
+      <c r="X28" s="15"/>
+      <c r="Y28" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="Z28" s="14"/>
-      <c r="AA28" s="14"/>
-      <c r="AB28" s="14"/>
-      <c r="AC28" s="14"/>
-      <c r="AD28" s="16" t="s">
+      <c r="Z28" s="15"/>
+      <c r="AA28" s="15"/>
+      <c r="AB28" s="15"/>
+      <c r="AC28" s="15"/>
+      <c r="AD28" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="AE28" s="16" t="s">
+      <c r="AE28" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="AF28" s="16"/>
-      <c r="AG28" s="16"/>
-      <c r="AH28" s="18" t="s">
+      <c r="AF28" s="17"/>
+      <c r="AG28" s="17"/>
+      <c r="AH28" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="AI28" s="18" t="s">
+      <c r="AI28" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="AJ28" s="18" t="s">
+      <c r="AJ28" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="AK28" s="18" t="s">
+      <c r="AK28" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="AL28" s="18"/>
-      <c r="AM28" s="18"/>
-      <c r="AN28" s="19" t="s">
-        <v>170</v>
-      </c>
-      <c r="AU28" s="20" t="s">
-        <v>160</v>
+      <c r="AL28" s="19"/>
+      <c r="AM28" s="19"/>
+      <c r="AN28" s="20" t="s">
+        <v>187</v>
+      </c>
+      <c r="AU28" s="21" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="B29" s="21" t="s">
+        <v>189</v>
+      </c>
+      <c r="B29" s="22" t="s">
         <v>41</v>
       </c>
       <c r="C29" s="1" t="s">
@@ -3561,23 +3646,23 @@
       <c r="D29" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="E29" s="21" t="s">
-        <v>172</v>
+      <c r="E29" s="10" t="s">
+        <v>190</v>
       </c>
       <c r="F29" s="11" t="n">
         <v>46027</v>
       </c>
-      <c r="I29" s="12" t="s">
+      <c r="I29" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="J29" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="K29" s="12" t="s">
+      <c r="J29" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="K29" s="13" t="s">
         <v>46</v>
       </c>
       <c r="P29" s="1" t="s">
-        <v>173</v>
+        <v>191</v>
       </c>
       <c r="Q29" s="8"/>
       <c r="R29" s="8"/>
@@ -3585,51 +3670,51 @@
       <c r="T29" s="8"/>
       <c r="U29" s="8"/>
       <c r="V29" s="8"/>
-      <c r="W29" s="14" t="s">
+      <c r="W29" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="X29" s="14"/>
-      <c r="Y29" s="14" t="s">
+      <c r="X29" s="15"/>
+      <c r="Y29" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="Z29" s="14"/>
-      <c r="AA29" s="14"/>
-      <c r="AB29" s="14"/>
-      <c r="AC29" s="14"/>
-      <c r="AD29" s="16" t="s">
+      <c r="Z29" s="15"/>
+      <c r="AA29" s="15"/>
+      <c r="AB29" s="15"/>
+      <c r="AC29" s="15"/>
+      <c r="AD29" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="AE29" s="16" t="s">
+      <c r="AE29" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="AF29" s="16"/>
-      <c r="AG29" s="16"/>
-      <c r="AH29" s="18" t="s">
+      <c r="AF29" s="17"/>
+      <c r="AG29" s="17"/>
+      <c r="AH29" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="AI29" s="18" t="s">
+      <c r="AI29" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="AJ29" s="18" t="s">
+      <c r="AJ29" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="AK29" s="18" t="s">
+      <c r="AK29" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="AL29" s="18"/>
-      <c r="AM29" s="18"/>
-      <c r="AN29" s="19" t="s">
-        <v>174</v>
-      </c>
-      <c r="AU29" s="20" t="s">
-        <v>175</v>
+      <c r="AL29" s="19"/>
+      <c r="AM29" s="19"/>
+      <c r="AN29" s="20" t="s">
+        <v>192</v>
+      </c>
+      <c r="AU29" s="21" t="s">
+        <v>193</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="B30" s="21" t="s">
+        <v>194</v>
+      </c>
+      <c r="B30" s="22" t="s">
         <v>41</v>
       </c>
       <c r="C30" s="1" t="s">
@@ -3638,23 +3723,23 @@
       <c r="D30" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="E30" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="F30" s="22" t="n">
+      <c r="E30" s="10" t="s">
+        <v>195</v>
+      </c>
+      <c r="F30" s="23" t="n">
         <v>46027</v>
       </c>
-      <c r="I30" s="12" t="s">
+      <c r="I30" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="J30" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="K30" s="12" t="s">
+      <c r="J30" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="K30" s="13" t="s">
         <v>46</v>
       </c>
       <c r="P30" s="1" t="s">
-        <v>178</v>
+        <v>196</v>
       </c>
       <c r="Q30" s="8"/>
       <c r="R30" s="8"/>
@@ -3662,51 +3747,51 @@
       <c r="T30" s="8"/>
       <c r="U30" s="8"/>
       <c r="V30" s="8"/>
-      <c r="W30" s="14" t="s">
+      <c r="W30" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="X30" s="14"/>
-      <c r="Y30" s="14" t="s">
+      <c r="X30" s="15"/>
+      <c r="Y30" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="Z30" s="14"/>
-      <c r="AA30" s="14"/>
-      <c r="AB30" s="14"/>
-      <c r="AC30" s="14"/>
-      <c r="AD30" s="16" t="s">
+      <c r="Z30" s="15"/>
+      <c r="AA30" s="15"/>
+      <c r="AB30" s="15"/>
+      <c r="AC30" s="15"/>
+      <c r="AD30" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="AE30" s="16" t="s">
+      <c r="AE30" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="AF30" s="16"/>
-      <c r="AG30" s="16"/>
-      <c r="AH30" s="18" t="s">
-        <v>91</v>
-      </c>
-      <c r="AI30" s="18" t="s">
+      <c r="AF30" s="17"/>
+      <c r="AG30" s="17"/>
+      <c r="AH30" s="19" t="s">
+        <v>95</v>
+      </c>
+      <c r="AI30" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="AJ30" s="18" t="s">
+      <c r="AJ30" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="AK30" s="18" t="s">
+      <c r="AK30" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="AL30" s="18"/>
-      <c r="AM30" s="18"/>
-      <c r="AN30" s="19" t="s">
-        <v>179</v>
-      </c>
-      <c r="AU30" s="20" t="s">
-        <v>164</v>
+      <c r="AL30" s="19"/>
+      <c r="AM30" s="19"/>
+      <c r="AN30" s="20" t="s">
+        <v>197</v>
+      </c>
+      <c r="AU30" s="21" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="B31" s="21" t="s">
+        <v>199</v>
+      </c>
+      <c r="B31" s="22" t="s">
         <v>41</v>
       </c>
       <c r="C31" s="1" t="s">
@@ -3715,23 +3800,23 @@
       <c r="D31" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="E31" s="21" t="s">
-        <v>181</v>
+      <c r="E31" s="10" t="s">
+        <v>200</v>
       </c>
       <c r="F31" s="11" t="n">
         <v>46027</v>
       </c>
-      <c r="I31" s="12" t="s">
+      <c r="I31" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="J31" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="K31" s="12" t="s">
+      <c r="J31" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="K31" s="13" t="s">
         <v>46</v>
       </c>
       <c r="P31" s="1" t="s">
-        <v>182</v>
+        <v>201</v>
       </c>
       <c r="Q31" s="8"/>
       <c r="R31" s="8"/>
@@ -3739,51 +3824,51 @@
       <c r="T31" s="8"/>
       <c r="U31" s="8"/>
       <c r="V31" s="8"/>
-      <c r="W31" s="14" t="s">
+      <c r="W31" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="X31" s="14"/>
-      <c r="Y31" s="14" t="s">
+      <c r="X31" s="15"/>
+      <c r="Y31" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="Z31" s="14"/>
-      <c r="AA31" s="14"/>
-      <c r="AB31" s="14"/>
-      <c r="AC31" s="14"/>
-      <c r="AD31" s="16" t="s">
+      <c r="Z31" s="15"/>
+      <c r="AA31" s="15"/>
+      <c r="AB31" s="15"/>
+      <c r="AC31" s="15"/>
+      <c r="AD31" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="AE31" s="16" t="s">
+      <c r="AE31" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="AF31" s="16"/>
-      <c r="AG31" s="16"/>
-      <c r="AH31" s="18" t="s">
+      <c r="AF31" s="17"/>
+      <c r="AG31" s="17"/>
+      <c r="AH31" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="AI31" s="18" t="s">
+      <c r="AI31" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="AJ31" s="18" t="s">
+      <c r="AJ31" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="AK31" s="18" t="s">
+      <c r="AK31" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="AL31" s="18"/>
-      <c r="AM31" s="18"/>
-      <c r="AN31" s="19" t="s">
-        <v>183</v>
-      </c>
-      <c r="AU31" s="20" t="s">
-        <v>168</v>
+      <c r="AL31" s="19"/>
+      <c r="AM31" s="19"/>
+      <c r="AN31" s="20" t="s">
+        <v>202</v>
+      </c>
+      <c r="AU31" s="21" t="s">
+        <v>203</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="B32" s="21" t="s">
+        <v>204</v>
+      </c>
+      <c r="B32" s="22" t="s">
         <v>41</v>
       </c>
       <c r="C32" s="1" t="s">
@@ -3792,23 +3877,23 @@
       <c r="D32" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="E32" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="F32" s="22" t="n">
+      <c r="E32" s="10" t="s">
+        <v>205</v>
+      </c>
+      <c r="F32" s="23" t="n">
         <v>46027</v>
       </c>
-      <c r="I32" s="12" t="s">
+      <c r="I32" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="J32" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="K32" s="12" t="s">
+      <c r="J32" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="K32" s="13" t="s">
         <v>46</v>
       </c>
       <c r="P32" s="1" t="s">
-        <v>186</v>
+        <v>206</v>
       </c>
       <c r="Q32" s="8"/>
       <c r="R32" s="8"/>
@@ -3816,51 +3901,51 @@
       <c r="T32" s="8"/>
       <c r="U32" s="8"/>
       <c r="V32" s="8"/>
-      <c r="W32" s="14" t="s">
+      <c r="W32" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="X32" s="14"/>
-      <c r="Y32" s="14" t="s">
+      <c r="X32" s="15"/>
+      <c r="Y32" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="Z32" s="14"/>
-      <c r="AA32" s="14"/>
-      <c r="AB32" s="14"/>
-      <c r="AC32" s="14"/>
-      <c r="AD32" s="16" t="s">
+      <c r="Z32" s="15"/>
+      <c r="AA32" s="15"/>
+      <c r="AB32" s="15"/>
+      <c r="AC32" s="15"/>
+      <c r="AD32" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="AE32" s="16" t="s">
+      <c r="AE32" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="AF32" s="16"/>
-      <c r="AG32" s="16"/>
-      <c r="AH32" s="18" t="s">
+      <c r="AF32" s="17"/>
+      <c r="AG32" s="17"/>
+      <c r="AH32" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="AI32" s="18" t="s">
+      <c r="AI32" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="AJ32" s="18" t="s">
+      <c r="AJ32" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="AK32" s="18" t="s">
+      <c r="AK32" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="AL32" s="18"/>
-      <c r="AM32" s="18"/>
-      <c r="AN32" s="19" t="s">
-        <v>187</v>
-      </c>
-      <c r="AU32" s="20" t="s">
-        <v>172</v>
+      <c r="AL32" s="19"/>
+      <c r="AM32" s="19"/>
+      <c r="AN32" s="20" t="s">
+        <v>207</v>
+      </c>
+      <c r="AU32" s="21" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="B33" s="21" t="s">
+        <v>209</v>
+      </c>
+      <c r="B33" s="22" t="s">
         <v>41</v>
       </c>
       <c r="C33" s="1" t="s">
@@ -3869,23 +3954,23 @@
       <c r="D33" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="E33" s="21" t="s">
-        <v>189</v>
+      <c r="E33" s="10" t="s">
+        <v>210</v>
       </c>
       <c r="F33" s="11" t="n">
         <v>46027</v>
       </c>
-      <c r="I33" s="12" t="s">
+      <c r="I33" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="J33" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="K33" s="12" t="s">
+      <c r="J33" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="K33" s="13" t="s">
         <v>46</v>
       </c>
       <c r="P33" s="1" t="s">
-        <v>190</v>
+        <v>211</v>
       </c>
       <c r="Q33" s="8"/>
       <c r="R33" s="8"/>
@@ -3893,51 +3978,51 @@
       <c r="T33" s="8"/>
       <c r="U33" s="8"/>
       <c r="V33" s="8"/>
-      <c r="W33" s="14" t="s">
+      <c r="W33" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="X33" s="14"/>
-      <c r="Y33" s="14" t="s">
+      <c r="X33" s="15"/>
+      <c r="Y33" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="Z33" s="14"/>
-      <c r="AA33" s="14"/>
-      <c r="AB33" s="14"/>
-      <c r="AC33" s="14"/>
-      <c r="AD33" s="16" t="s">
+      <c r="Z33" s="15"/>
+      <c r="AA33" s="15"/>
+      <c r="AB33" s="15"/>
+      <c r="AC33" s="15"/>
+      <c r="AD33" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="AE33" s="16" t="s">
+      <c r="AE33" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="AF33" s="16"/>
-      <c r="AG33" s="16"/>
-      <c r="AH33" s="18" t="s">
+      <c r="AF33" s="17"/>
+      <c r="AG33" s="17"/>
+      <c r="AH33" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="AI33" s="18" t="s">
+      <c r="AI33" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="AJ33" s="18" t="s">
+      <c r="AJ33" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="AK33" s="18" t="s">
+      <c r="AK33" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="AL33" s="18"/>
-      <c r="AM33" s="18"/>
-      <c r="AN33" s="19" t="s">
-        <v>191</v>
-      </c>
-      <c r="AU33" s="20" t="s">
-        <v>177</v>
+      <c r="AL33" s="19"/>
+      <c r="AM33" s="19"/>
+      <c r="AN33" s="20" t="s">
+        <v>212</v>
+      </c>
+      <c r="AU33" s="21" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="B34" s="21" t="s">
+        <v>214</v>
+      </c>
+      <c r="B34" s="22" t="s">
         <v>41</v>
       </c>
       <c r="C34" s="1" t="s">
@@ -3946,23 +4031,23 @@
       <c r="D34" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="E34" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="F34" s="22" t="n">
+      <c r="E34" s="10" t="s">
+        <v>210</v>
+      </c>
+      <c r="F34" s="23" t="n">
         <v>46027</v>
       </c>
-      <c r="I34" s="12" t="s">
+      <c r="I34" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="K34" s="12" t="s">
+      <c r="J34" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="K34" s="13" t="s">
         <v>46</v>
       </c>
       <c r="P34" s="1" t="s">
-        <v>194</v>
+        <v>215</v>
       </c>
       <c r="Q34" s="8"/>
       <c r="R34" s="8"/>
@@ -3970,51 +4055,51 @@
       <c r="T34" s="8"/>
       <c r="U34" s="8"/>
       <c r="V34" s="8"/>
-      <c r="W34" s="14" t="s">
+      <c r="W34" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="X34" s="14"/>
-      <c r="Y34" s="14" t="s">
+      <c r="X34" s="15"/>
+      <c r="Y34" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="Z34" s="14"/>
-      <c r="AA34" s="14"/>
-      <c r="AB34" s="14"/>
-      <c r="AC34" s="14"/>
-      <c r="AD34" s="16" t="s">
+      <c r="Z34" s="15"/>
+      <c r="AA34" s="15"/>
+      <c r="AB34" s="15"/>
+      <c r="AC34" s="15"/>
+      <c r="AD34" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="AE34" s="16" t="s">
+      <c r="AE34" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="AF34" s="16"/>
-      <c r="AG34" s="16"/>
-      <c r="AH34" s="18" t="s">
-        <v>91</v>
-      </c>
-      <c r="AI34" s="18" t="s">
+      <c r="AF34" s="17"/>
+      <c r="AG34" s="17"/>
+      <c r="AH34" s="19" t="s">
+        <v>95</v>
+      </c>
+      <c r="AI34" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="AJ34" s="18" t="s">
+      <c r="AJ34" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="AK34" s="18" t="s">
+      <c r="AK34" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="AL34" s="18"/>
-      <c r="AM34" s="18"/>
-      <c r="AN34" s="19" t="s">
-        <v>195</v>
-      </c>
-      <c r="AU34" s="20" t="s">
-        <v>181</v>
+      <c r="AL34" s="19"/>
+      <c r="AM34" s="19"/>
+      <c r="AN34" s="20" t="s">
+        <v>216</v>
+      </c>
+      <c r="AU34" s="21" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="B35" s="21" t="s">
+        <v>218</v>
+      </c>
+      <c r="B35" s="22" t="s">
         <v>41</v>
       </c>
       <c r="C35" s="1" t="s">
@@ -4023,23 +4108,23 @@
       <c r="D35" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="E35" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="F35" s="22" t="n">
+      <c r="E35" s="10" t="s">
+        <v>210</v>
+      </c>
+      <c r="F35" s="23" t="n">
         <v>46027</v>
       </c>
-      <c r="I35" s="12" t="s">
+      <c r="I35" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="J35" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="K35" s="12" t="s">
+      <c r="J35" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="K35" s="13" t="s">
         <v>46</v>
       </c>
       <c r="P35" s="1" t="s">
-        <v>198</v>
+        <v>219</v>
       </c>
       <c r="Q35" s="8"/>
       <c r="R35" s="8"/>
@@ -4047,51 +4132,51 @@
       <c r="T35" s="8"/>
       <c r="U35" s="8"/>
       <c r="V35" s="8"/>
-      <c r="W35" s="14" t="s">
+      <c r="W35" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="X35" s="14"/>
-      <c r="Y35" s="14" t="s">
+      <c r="X35" s="15"/>
+      <c r="Y35" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="Z35" s="14"/>
-      <c r="AA35" s="14"/>
-      <c r="AB35" s="14"/>
-      <c r="AC35" s="14"/>
-      <c r="AD35" s="16" t="s">
+      <c r="Z35" s="15"/>
+      <c r="AA35" s="15"/>
+      <c r="AB35" s="15"/>
+      <c r="AC35" s="15"/>
+      <c r="AD35" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="AE35" s="16" t="s">
+      <c r="AE35" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="AF35" s="16"/>
-      <c r="AG35" s="16"/>
-      <c r="AH35" s="18" t="s">
+      <c r="AF35" s="17"/>
+      <c r="AG35" s="17"/>
+      <c r="AH35" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="AI35" s="18" t="s">
+      <c r="AI35" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="AJ35" s="18" t="s">
+      <c r="AJ35" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="AK35" s="18" t="s">
+      <c r="AK35" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="AL35" s="18"/>
-      <c r="AM35" s="18"/>
-      <c r="AN35" s="19" t="s">
-        <v>199</v>
-      </c>
-      <c r="AU35" s="20" t="s">
-        <v>189</v>
+      <c r="AL35" s="19"/>
+      <c r="AM35" s="19"/>
+      <c r="AN35" s="20" t="s">
+        <v>220</v>
+      </c>
+      <c r="AU35" s="21" t="s">
+        <v>221</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="B36" s="21" t="s">
+        <v>222</v>
+      </c>
+      <c r="B36" s="22" t="s">
         <v>41</v>
       </c>
       <c r="C36" s="1" t="s">
@@ -4100,23 +4185,23 @@
       <c r="D36" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="E36" s="21" t="s">
-        <v>201</v>
+      <c r="E36" s="10" t="s">
+        <v>210</v>
       </c>
       <c r="F36" s="11" t="n">
         <v>46027</v>
       </c>
-      <c r="I36" s="12" t="s">
+      <c r="I36" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="J36" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="K36" s="12" t="s">
+      <c r="J36" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="K36" s="13" t="s">
         <v>46</v>
       </c>
       <c r="P36" s="1" t="s">
-        <v>202</v>
+        <v>223</v>
       </c>
       <c r="Q36" s="8"/>
       <c r="R36" s="8"/>
@@ -4124,51 +4209,51 @@
       <c r="T36" s="8"/>
       <c r="U36" s="8"/>
       <c r="V36" s="8"/>
-      <c r="W36" s="14" t="s">
+      <c r="W36" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="X36" s="14"/>
-      <c r="Y36" s="14" t="s">
+      <c r="X36" s="15"/>
+      <c r="Y36" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="Z36" s="14"/>
-      <c r="AA36" s="14"/>
-      <c r="AB36" s="14"/>
-      <c r="AC36" s="14"/>
-      <c r="AD36" s="16" t="s">
+      <c r="Z36" s="15"/>
+      <c r="AA36" s="15"/>
+      <c r="AB36" s="15"/>
+      <c r="AC36" s="15"/>
+      <c r="AD36" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="AE36" s="16" t="s">
+      <c r="AE36" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="AF36" s="16"/>
-      <c r="AG36" s="16"/>
-      <c r="AH36" s="18" t="s">
+      <c r="AF36" s="17"/>
+      <c r="AG36" s="17"/>
+      <c r="AH36" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="AI36" s="18" t="s">
+      <c r="AI36" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="AJ36" s="18" t="s">
+      <c r="AJ36" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="AK36" s="18" t="s">
+      <c r="AK36" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="AL36" s="18"/>
-      <c r="AM36" s="18"/>
-      <c r="AN36" s="19" t="s">
-        <v>203</v>
-      </c>
-      <c r="AU36" s="20" t="s">
-        <v>193</v>
+      <c r="AL36" s="19"/>
+      <c r="AM36" s="19"/>
+      <c r="AN36" s="20" t="s">
+        <v>224</v>
+      </c>
+      <c r="AU36" s="21" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="B37" s="21" t="s">
+        <v>226</v>
+      </c>
+      <c r="B37" s="22" t="s">
         <v>41</v>
       </c>
       <c r="C37" s="1" t="s">
@@ -4177,69 +4262,99 @@
       <c r="D37" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="E37" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="F37" s="22" t="n">
+      <c r="E37" s="10" t="s">
+        <v>227</v>
+      </c>
+      <c r="F37" s="23" t="n">
         <v>46027</v>
       </c>
-      <c r="I37" s="12" t="s">
+      <c r="I37" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="J37" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="K37" s="12" t="s">
+      <c r="J37" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="K37" s="13" t="s">
         <v>46</v>
       </c>
       <c r="P37" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="Q37" s="23"/>
-      <c r="R37" s="23"/>
-      <c r="S37" s="23"/>
-      <c r="T37" s="23"/>
-      <c r="U37" s="23"/>
-      <c r="V37" s="23"/>
-      <c r="W37" s="14" t="s">
-        <v>207</v>
-      </c>
-      <c r="X37" s="14"/>
-      <c r="Y37" s="14" t="s">
+        <v>228</v>
+      </c>
+      <c r="Q37" s="24"/>
+      <c r="R37" s="24"/>
+      <c r="S37" s="24"/>
+      <c r="T37" s="24"/>
+      <c r="U37" s="24"/>
+      <c r="V37" s="24"/>
+      <c r="W37" s="15" t="s">
+        <v>229</v>
+      </c>
+      <c r="X37" s="15"/>
+      <c r="Y37" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="Z37" s="14"/>
-      <c r="AA37" s="14"/>
-      <c r="AB37" s="14"/>
-      <c r="AC37" s="14"/>
-      <c r="AD37" s="16" t="s">
-        <v>208</v>
-      </c>
-      <c r="AE37" s="16" t="s">
-        <v>209</v>
-      </c>
-      <c r="AF37" s="16"/>
-      <c r="AG37" s="16"/>
-      <c r="AH37" s="18" t="s">
-        <v>91</v>
-      </c>
-      <c r="AI37" s="18" t="s">
+      <c r="Z37" s="15"/>
+      <c r="AA37" s="15"/>
+      <c r="AB37" s="15"/>
+      <c r="AC37" s="15"/>
+      <c r="AD37" s="17" t="s">
+        <v>230</v>
+      </c>
+      <c r="AE37" s="17" t="s">
+        <v>231</v>
+      </c>
+      <c r="AF37" s="17"/>
+      <c r="AG37" s="17"/>
+      <c r="AH37" s="19" t="s">
+        <v>95</v>
+      </c>
+      <c r="AI37" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="AJ37" s="18" t="s">
+      <c r="AJ37" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="AK37" s="18" t="s">
+      <c r="AK37" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="AL37" s="24"/>
-      <c r="AM37" s="24"/>
-      <c r="AN37" s="19" t="s">
-        <v>203</v>
-      </c>
-      <c r="AU37" s="20" t="s">
-        <v>210</v>
-      </c>
+      <c r="AL37" s="25"/>
+      <c r="AM37" s="25"/>
+      <c r="AN37" s="20" t="s">
+        <v>224</v>
+      </c>
+      <c r="AU37" s="21" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E38" s="10"/>
+    </row>
+    <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E39" s="10"/>
+    </row>
+    <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E40" s="10"/>
+    </row>
+    <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E41" s="10"/>
+    </row>
+    <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E42" s="10"/>
+    </row>
+    <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E43" s="10"/>
+    </row>
+    <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E44" s="10"/>
+    </row>
+    <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E45" s="10"/>
+    </row>
+    <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E46" s="10"/>
+    </row>
+    <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E47" s="10"/>
     </row>
     <row r="1048572" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -4388,10 +4503,10 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="21" t="s">
-        <v>211</v>
-      </c>
-      <c r="B2" s="21" t="s">
+      <c r="A2" s="22" t="s">
+        <v>233</v>
+      </c>
+      <c r="B2" s="22" t="s">
         <v>41</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -4400,21 +4515,21 @@
       <c r="D2" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="E2" s="21" t="s">
-        <v>212</v>
+      <c r="E2" s="22" t="s">
+        <v>234</v>
       </c>
       <c r="F2" s="11" t="n">
         <v>46027</v>
       </c>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
-      <c r="I2" s="12" t="s">
+      <c r="I2" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="J2" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="K2" s="12" t="s">
+      <c r="J2" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="K2" s="13" t="s">
         <v>46</v>
       </c>
       <c r="L2" s="1"/>
@@ -4422,7 +4537,7 @@
       <c r="N2" s="1"/>
       <c r="O2" s="1"/>
       <c r="P2" s="8" t="s">
-        <v>213</v>
+        <v>235</v>
       </c>
       <c r="Q2" s="8"/>
       <c r="R2" s="8"/>
@@ -4430,41 +4545,41 @@
       <c r="T2" s="8"/>
       <c r="U2" s="8"/>
       <c r="V2" s="8"/>
-      <c r="W2" s="14" t="s">
+      <c r="W2" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="X2" s="14"/>
-      <c r="Y2" s="14" t="s">
+      <c r="X2" s="15"/>
+      <c r="Y2" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="Z2" s="14"/>
-      <c r="AA2" s="14"/>
-      <c r="AB2" s="14"/>
-      <c r="AC2" s="14"/>
-      <c r="AD2" s="16" t="s">
+      <c r="Z2" s="15"/>
+      <c r="AA2" s="15"/>
+      <c r="AB2" s="15"/>
+      <c r="AC2" s="15"/>
+      <c r="AD2" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="AE2" s="16" t="s">
+      <c r="AE2" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="AF2" s="16"/>
-      <c r="AG2" s="16"/>
-      <c r="AH2" s="18" t="s">
+      <c r="AF2" s="17"/>
+      <c r="AG2" s="17"/>
+      <c r="AH2" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="AI2" s="18" t="s">
+      <c r="AI2" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="AJ2" s="18" t="s">
+      <c r="AJ2" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="AK2" s="18" t="s">
+      <c r="AK2" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="AL2" s="18"/>
-      <c r="AM2" s="18"/>
-      <c r="AN2" s="19" t="s">
-        <v>136</v>
+      <c r="AL2" s="19"/>
+      <c r="AM2" s="19"/>
+      <c r="AN2" s="20" t="s">
+        <v>147</v>
       </c>
     </row>
   </sheetData>
@@ -4486,9 +4601,9 @@
   <dimension ref="A1:AN6"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="25" width="11.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="25" width="15.56"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="25" width="18.22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="26" width="11.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="26" width="15.56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="26" width="18.22"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4614,8 +4729,8 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="20" t="s">
-        <v>214</v>
+      <c r="A2" s="21" t="s">
+        <v>236</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>41</v>
@@ -4627,28 +4742,28 @@
         <v>43</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>215</v>
+        <v>237</v>
       </c>
       <c r="F2" s="11" t="n">
         <v>46031</v>
       </c>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
-      <c r="I2" s="12" t="s">
+      <c r="I2" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="J2" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="K2" s="12" t="s">
+      <c r="J2" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="K2" s="13" t="s">
         <v>46</v>
       </c>
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
       <c r="N2" s="1"/>
       <c r="O2" s="1"/>
-      <c r="P2" s="20" t="s">
-        <v>216</v>
+      <c r="P2" s="21" t="s">
+        <v>238</v>
       </c>
       <c r="Q2" s="8"/>
       <c r="R2" s="8"/>
@@ -4656,48 +4771,48 @@
       <c r="T2" s="8"/>
       <c r="U2" s="8"/>
       <c r="V2" s="8"/>
-      <c r="W2" s="14" t="s">
-        <v>207</v>
-      </c>
-      <c r="X2" s="14"/>
-      <c r="Y2" s="14" t="s">
+      <c r="W2" s="15" t="s">
+        <v>229</v>
+      </c>
+      <c r="X2" s="15"/>
+      <c r="Y2" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="Z2" s="14"/>
-      <c r="AA2" s="14"/>
-      <c r="AB2" s="14"/>
-      <c r="AC2" s="14"/>
-      <c r="AD2" s="16" t="s">
-        <v>208</v>
-      </c>
-      <c r="AE2" s="16" t="s">
-        <v>217</v>
-      </c>
-      <c r="AF2" s="16"/>
-      <c r="AG2" s="16"/>
-      <c r="AH2" s="18" t="s">
+      <c r="Z2" s="15"/>
+      <c r="AA2" s="15"/>
+      <c r="AB2" s="15"/>
+      <c r="AC2" s="15"/>
+      <c r="AD2" s="17" t="s">
+        <v>230</v>
+      </c>
+      <c r="AE2" s="17" t="s">
+        <v>239</v>
+      </c>
+      <c r="AF2" s="17"/>
+      <c r="AG2" s="17"/>
+      <c r="AH2" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="AI2" s="18" t="s">
+      <c r="AI2" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="AJ2" s="18" t="s">
-        <v>218</v>
-      </c>
-      <c r="AK2" s="18" t="s">
+      <c r="AJ2" s="19" t="s">
+        <v>240</v>
+      </c>
+      <c r="AK2" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="AL2" s="18"/>
-      <c r="AM2" s="18"/>
-      <c r="AN2" s="19" t="s">
-        <v>219</v>
+      <c r="AL2" s="19"/>
+      <c r="AM2" s="19"/>
+      <c r="AN2" s="20" t="s">
+        <v>241</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="20" t="s">
-        <v>220</v>
-      </c>
-      <c r="B3" s="20" t="s">
+      <c r="A3" s="21" t="s">
+        <v>242</v>
+      </c>
+      <c r="B3" s="21" t="s">
         <v>41</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -4707,28 +4822,28 @@
         <v>43</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>221</v>
+        <v>243</v>
       </c>
       <c r="F3" s="11" t="n">
         <v>46031</v>
       </c>
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
-      <c r="I3" s="12" t="s">
+      <c r="I3" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="J3" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="K3" s="12" t="s">
+      <c r="J3" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="K3" s="13" t="s">
         <v>46</v>
       </c>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
       <c r="N3" s="1"/>
       <c r="O3" s="1"/>
-      <c r="P3" s="20" t="s">
-        <v>222</v>
+      <c r="P3" s="21" t="s">
+        <v>244</v>
       </c>
       <c r="Q3" s="8"/>
       <c r="R3" s="8"/>
@@ -4736,48 +4851,48 @@
       <c r="T3" s="8"/>
       <c r="U3" s="8"/>
       <c r="V3" s="8"/>
-      <c r="W3" s="14" t="s">
-        <v>207</v>
-      </c>
-      <c r="X3" s="14"/>
-      <c r="Y3" s="14" t="s">
+      <c r="W3" s="15" t="s">
+        <v>229</v>
+      </c>
+      <c r="X3" s="15"/>
+      <c r="Y3" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="Z3" s="14"/>
-      <c r="AA3" s="14"/>
-      <c r="AB3" s="14"/>
-      <c r="AC3" s="14"/>
-      <c r="AD3" s="16" t="s">
-        <v>208</v>
-      </c>
-      <c r="AE3" s="16" t="s">
-        <v>217</v>
-      </c>
-      <c r="AF3" s="16"/>
-      <c r="AG3" s="16"/>
-      <c r="AH3" s="18" t="s">
+      <c r="Z3" s="15"/>
+      <c r="AA3" s="15"/>
+      <c r="AB3" s="15"/>
+      <c r="AC3" s="15"/>
+      <c r="AD3" s="17" t="s">
+        <v>230</v>
+      </c>
+      <c r="AE3" s="17" t="s">
+        <v>239</v>
+      </c>
+      <c r="AF3" s="17"/>
+      <c r="AG3" s="17"/>
+      <c r="AH3" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="AI3" s="18" t="s">
+      <c r="AI3" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="AJ3" s="18" t="s">
+      <c r="AJ3" s="19" t="s">
         <v>65</v>
       </c>
-      <c r="AK3" s="18" t="s">
+      <c r="AK3" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="AL3" s="18"/>
-      <c r="AM3" s="18"/>
-      <c r="AN3" s="19" t="s">
-        <v>219</v>
+      <c r="AL3" s="19"/>
+      <c r="AM3" s="19"/>
+      <c r="AN3" s="20" t="s">
+        <v>241</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="20" t="s">
-        <v>223</v>
-      </c>
-      <c r="B4" s="20" t="s">
+      <c r="A4" s="21" t="s">
+        <v>245</v>
+      </c>
+      <c r="B4" s="21" t="s">
         <v>41</v>
       </c>
       <c r="C4" s="1" t="s">
@@ -4787,28 +4902,28 @@
         <v>43</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>224</v>
+        <v>246</v>
       </c>
       <c r="F4" s="11" t="n">
         <v>46031</v>
       </c>
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
-      <c r="I4" s="12" t="s">
+      <c r="I4" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="J4" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="K4" s="12" t="s">
+      <c r="J4" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="K4" s="13" t="s">
         <v>46</v>
       </c>
       <c r="L4" s="1"/>
       <c r="M4" s="1"/>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
-      <c r="P4" s="20" t="s">
-        <v>225</v>
+      <c r="P4" s="21" t="s">
+        <v>247</v>
       </c>
       <c r="Q4" s="8"/>
       <c r="R4" s="8"/>
@@ -4816,48 +4931,48 @@
       <c r="T4" s="8"/>
       <c r="U4" s="8"/>
       <c r="V4" s="8"/>
-      <c r="W4" s="14" t="s">
-        <v>207</v>
-      </c>
-      <c r="X4" s="14"/>
-      <c r="Y4" s="14" t="s">
+      <c r="W4" s="15" t="s">
+        <v>229</v>
+      </c>
+      <c r="X4" s="15"/>
+      <c r="Y4" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="Z4" s="14"/>
-      <c r="AA4" s="14"/>
-      <c r="AB4" s="14"/>
-      <c r="AC4" s="14"/>
-      <c r="AD4" s="16" t="s">
-        <v>208</v>
-      </c>
-      <c r="AE4" s="16" t="s">
-        <v>217</v>
-      </c>
-      <c r="AF4" s="16"/>
-      <c r="AG4" s="16"/>
-      <c r="AH4" s="18" t="s">
+      <c r="Z4" s="15"/>
+      <c r="AA4" s="15"/>
+      <c r="AB4" s="15"/>
+      <c r="AC4" s="15"/>
+      <c r="AD4" s="17" t="s">
+        <v>230</v>
+      </c>
+      <c r="AE4" s="17" t="s">
+        <v>239</v>
+      </c>
+      <c r="AF4" s="17"/>
+      <c r="AG4" s="17"/>
+      <c r="AH4" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="AI4" s="18" t="s">
+      <c r="AI4" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="AJ4" s="18" t="s">
+      <c r="AJ4" s="19" t="s">
         <v>65</v>
       </c>
-      <c r="AK4" s="18" t="s">
+      <c r="AK4" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="AL4" s="18"/>
-      <c r="AM4" s="18"/>
-      <c r="AN4" s="19" t="s">
-        <v>219</v>
+      <c r="AL4" s="19"/>
+      <c r="AM4" s="19"/>
+      <c r="AN4" s="20" t="s">
+        <v>241</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="20" t="s">
-        <v>226</v>
-      </c>
-      <c r="B5" s="20" t="s">
+      <c r="A5" s="21" t="s">
+        <v>248</v>
+      </c>
+      <c r="B5" s="21" t="s">
         <v>41</v>
       </c>
       <c r="C5" s="1" t="s">
@@ -4867,20 +4982,20 @@
         <v>43</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>201</v>
+        <v>249</v>
       </c>
       <c r="F5" s="11" t="n">
         <v>46031</v>
       </c>
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
-      <c r="I5" s="12" t="s">
+      <c r="I5" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="J5" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="K5" s="12" t="s">
+      <c r="J5" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="K5" s="13" t="s">
         <v>46</v>
       </c>
       <c r="L5" s="1"/>
@@ -4888,7 +5003,7 @@
       <c r="N5" s="1"/>
       <c r="O5" s="1"/>
       <c r="P5" s="1" t="s">
-        <v>227</v>
+        <v>250</v>
       </c>
       <c r="Q5" s="8"/>
       <c r="R5" s="8"/>
@@ -4896,48 +5011,48 @@
       <c r="T5" s="8"/>
       <c r="U5" s="8"/>
       <c r="V5" s="8"/>
-      <c r="W5" s="14" t="s">
-        <v>207</v>
-      </c>
-      <c r="X5" s="14"/>
-      <c r="Y5" s="14" t="s">
+      <c r="W5" s="15" t="s">
+        <v>229</v>
+      </c>
+      <c r="X5" s="15"/>
+      <c r="Y5" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="Z5" s="14"/>
-      <c r="AA5" s="14"/>
-      <c r="AB5" s="14"/>
-      <c r="AC5" s="14"/>
-      <c r="AD5" s="16" t="s">
-        <v>208</v>
-      </c>
-      <c r="AE5" s="16" t="s">
-        <v>228</v>
-      </c>
-      <c r="AF5" s="16"/>
-      <c r="AG5" s="16"/>
-      <c r="AH5" s="18" t="s">
+      <c r="Z5" s="15"/>
+      <c r="AA5" s="15"/>
+      <c r="AB5" s="15"/>
+      <c r="AC5" s="15"/>
+      <c r="AD5" s="17" t="s">
+        <v>230</v>
+      </c>
+      <c r="AE5" s="17" t="s">
+        <v>251</v>
+      </c>
+      <c r="AF5" s="17"/>
+      <c r="AG5" s="17"/>
+      <c r="AH5" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="AI5" s="18" t="s">
+      <c r="AI5" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="AJ5" s="18" t="s">
+      <c r="AJ5" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="AK5" s="18" t="s">
+      <c r="AK5" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="AL5" s="18"/>
-      <c r="AM5" s="18"/>
-      <c r="AN5" s="19" t="s">
+      <c r="AL5" s="19"/>
+      <c r="AM5" s="19"/>
+      <c r="AN5" s="20" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="20" t="s">
-        <v>229</v>
-      </c>
-      <c r="B6" s="20" t="s">
+      <c r="A6" s="21" t="s">
+        <v>252</v>
+      </c>
+      <c r="B6" s="21" t="s">
         <v>41</v>
       </c>
       <c r="C6" s="1" t="s">
@@ -4947,20 +5062,20 @@
         <v>43</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>155</v>
+        <v>183</v>
       </c>
       <c r="F6" s="11" t="n">
         <v>46031</v>
       </c>
       <c r="G6" s="1"/>
       <c r="H6" s="1"/>
-      <c r="I6" s="12" t="s">
+      <c r="I6" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="J6" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="K6" s="12" t="s">
+      <c r="J6" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="K6" s="13" t="s">
         <v>46</v>
       </c>
       <c r="L6" s="1"/>
@@ -4968,7 +5083,7 @@
       <c r="N6" s="1"/>
       <c r="O6" s="1"/>
       <c r="P6" s="1" t="s">
-        <v>230</v>
+        <v>253</v>
       </c>
       <c r="Q6" s="8"/>
       <c r="R6" s="8"/>
@@ -4976,40 +5091,40 @@
       <c r="T6" s="8"/>
       <c r="U6" s="8"/>
       <c r="V6" s="8"/>
-      <c r="W6" s="14" t="s">
-        <v>231</v>
-      </c>
-      <c r="X6" s="14"/>
-      <c r="Y6" s="14" t="s">
+      <c r="W6" s="15" t="s">
+        <v>254</v>
+      </c>
+      <c r="X6" s="15"/>
+      <c r="Y6" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="Z6" s="14"/>
-      <c r="AA6" s="14"/>
-      <c r="AB6" s="14"/>
-      <c r="AC6" s="14"/>
-      <c r="AD6" s="16" t="s">
-        <v>208</v>
-      </c>
-      <c r="AE6" s="16" t="s">
-        <v>228</v>
-      </c>
-      <c r="AF6" s="16"/>
-      <c r="AG6" s="16"/>
-      <c r="AH6" s="18" t="s">
+      <c r="Z6" s="15"/>
+      <c r="AA6" s="15"/>
+      <c r="AB6" s="15"/>
+      <c r="AC6" s="15"/>
+      <c r="AD6" s="17" t="s">
+        <v>230</v>
+      </c>
+      <c r="AE6" s="17" t="s">
+        <v>251</v>
+      </c>
+      <c r="AF6" s="17"/>
+      <c r="AG6" s="17"/>
+      <c r="AH6" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="AI6" s="18" t="s">
+      <c r="AI6" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="AJ6" s="18" t="s">
+      <c r="AJ6" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="AK6" s="18" t="s">
+      <c r="AK6" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="AL6" s="18"/>
-      <c r="AM6" s="18"/>
-      <c r="AN6" s="19" t="s">
+      <c r="AL6" s="19"/>
+      <c r="AM6" s="19"/>
+      <c r="AN6" s="20" t="s">
         <v>56</v>
       </c>
     </row>
@@ -5034,7 +5149,7 @@
   <sheetData>
     <row r="4" s="1" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>232</v>
+        <v>255</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>41</v>
@@ -5045,23 +5160,23 @@
       <c r="D4" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="E4" s="21" t="s">
-        <v>233</v>
+      <c r="E4" s="22" t="s">
+        <v>256</v>
       </c>
       <c r="F4" s="11" t="n">
         <v>46027</v>
       </c>
-      <c r="I4" s="12" t="s">
+      <c r="I4" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="J4" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="K4" s="12" t="s">
+      <c r="J4" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="K4" s="13" t="s">
         <v>46</v>
       </c>
       <c r="P4" s="1" t="s">
-        <v>234</v>
+        <v>257</v>
       </c>
       <c r="Q4" s="8"/>
       <c r="R4" s="8"/>
@@ -5069,51 +5184,51 @@
       <c r="T4" s="8"/>
       <c r="U4" s="8"/>
       <c r="V4" s="8"/>
-      <c r="W4" s="14" t="s">
+      <c r="W4" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="X4" s="14"/>
-      <c r="Y4" s="14" t="s">
+      <c r="X4" s="15"/>
+      <c r="Y4" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="Z4" s="14"/>
-      <c r="AA4" s="14"/>
-      <c r="AB4" s="14"/>
-      <c r="AC4" s="14"/>
-      <c r="AD4" s="16" t="s">
+      <c r="Z4" s="15"/>
+      <c r="AA4" s="15"/>
+      <c r="AB4" s="15"/>
+      <c r="AC4" s="15"/>
+      <c r="AD4" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="AE4" s="16" t="s">
+      <c r="AE4" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="AF4" s="16"/>
-      <c r="AG4" s="16"/>
-      <c r="AH4" s="18" t="s">
+      <c r="AF4" s="17"/>
+      <c r="AG4" s="17"/>
+      <c r="AH4" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="AI4" s="18" t="s">
+      <c r="AI4" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="AJ4" s="18" t="s">
+      <c r="AJ4" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="AK4" s="18" t="s">
+      <c r="AK4" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="AL4" s="18"/>
-      <c r="AM4" s="18"/>
-      <c r="AN4" s="19" t="s">
-        <v>219</v>
-      </c>
-      <c r="AU4" s="20" t="s">
-        <v>197</v>
+      <c r="AL4" s="19"/>
+      <c r="AM4" s="19"/>
+      <c r="AN4" s="20" t="s">
+        <v>241</v>
+      </c>
+      <c r="AU4" s="21" t="s">
+        <v>258</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="B6" s="21" t="s">
+        <v>259</v>
+      </c>
+      <c r="B6" s="22" t="s">
         <v>41</v>
       </c>
       <c r="C6" s="1" t="s">
@@ -5123,20 +5238,20 @@
         <v>43</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="F6" s="22" t="n">
+        <v>142</v>
+      </c>
+      <c r="F6" s="23" t="n">
         <v>46027</v>
       </c>
       <c r="G6" s="1"/>
       <c r="H6" s="1"/>
-      <c r="I6" s="12" t="s">
+      <c r="I6" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="J6" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="K6" s="12" t="s">
+      <c r="J6" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="K6" s="13" t="s">
         <v>46</v>
       </c>
       <c r="L6" s="1"/>
@@ -5144,7 +5259,7 @@
       <c r="N6" s="1"/>
       <c r="O6" s="1"/>
       <c r="P6" s="1" t="s">
-        <v>236</v>
+        <v>260</v>
       </c>
       <c r="Q6" s="8"/>
       <c r="R6" s="8"/>
@@ -5152,41 +5267,41 @@
       <c r="T6" s="8"/>
       <c r="U6" s="8"/>
       <c r="V6" s="8"/>
-      <c r="W6" s="14" t="s">
+      <c r="W6" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="X6" s="14"/>
-      <c r="Y6" s="14" t="s">
+      <c r="X6" s="15"/>
+      <c r="Y6" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="Z6" s="14"/>
-      <c r="AA6" s="14"/>
-      <c r="AB6" s="14"/>
-      <c r="AC6" s="14"/>
-      <c r="AD6" s="16" t="s">
+      <c r="Z6" s="15"/>
+      <c r="AA6" s="15"/>
+      <c r="AB6" s="15"/>
+      <c r="AC6" s="15"/>
+      <c r="AD6" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="AE6" s="16" t="s">
+      <c r="AE6" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="AF6" s="16"/>
-      <c r="AG6" s="16"/>
-      <c r="AH6" s="18" t="s">
+      <c r="AF6" s="17"/>
+      <c r="AG6" s="17"/>
+      <c r="AH6" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="AI6" s="18" t="s">
+      <c r="AI6" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="AJ6" s="18" t="s">
+      <c r="AJ6" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="AK6" s="18" t="s">
+      <c r="AK6" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="AL6" s="18"/>
-      <c r="AM6" s="18"/>
-      <c r="AN6" s="19" t="s">
-        <v>237</v>
+      <c r="AL6" s="19"/>
+      <c r="AM6" s="19"/>
+      <c r="AN6" s="20" t="s">
+        <v>261</v>
       </c>
       <c r="AO6" s="1"/>
       <c r="AP6" s="1"/>
@@ -5194,15 +5309,15 @@
       <c r="AR6" s="1"/>
       <c r="AS6" s="1"/>
       <c r="AT6" s="1"/>
-      <c r="AU6" s="20" t="s">
-        <v>116</v>
+      <c r="AU6" s="21" t="s">
+        <v>262</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="B8" s="21" t="s">
+        <v>263</v>
+      </c>
+      <c r="B8" s="22" t="s">
         <v>41</v>
       </c>
       <c r="C8" s="1" t="s">
@@ -5211,21 +5326,21 @@
       <c r="D8" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="E8" s="21" t="s">
-        <v>158</v>
+      <c r="E8" s="22" t="s">
+        <v>173</v>
       </c>
       <c r="F8" s="11" t="n">
         <v>46027</v>
       </c>
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
-      <c r="I8" s="12" t="s">
+      <c r="I8" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="J8" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="K8" s="12" t="s">
+      <c r="J8" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="K8" s="13" t="s">
         <v>46</v>
       </c>
       <c r="L8" s="1"/>
@@ -5233,7 +5348,7 @@
       <c r="N8" s="1"/>
       <c r="O8" s="1"/>
       <c r="P8" s="1" t="s">
-        <v>239</v>
+        <v>264</v>
       </c>
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
@@ -5241,41 +5356,41 @@
       <c r="T8" s="8"/>
       <c r="U8" s="8"/>
       <c r="V8" s="8"/>
-      <c r="W8" s="14" t="s">
+      <c r="W8" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="X8" s="14"/>
-      <c r="Y8" s="14" t="s">
+      <c r="X8" s="15"/>
+      <c r="Y8" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="Z8" s="14"/>
-      <c r="AA8" s="14"/>
-      <c r="AB8" s="14"/>
-      <c r="AC8" s="14"/>
-      <c r="AD8" s="16" t="s">
+      <c r="Z8" s="15"/>
+      <c r="AA8" s="15"/>
+      <c r="AB8" s="15"/>
+      <c r="AC8" s="15"/>
+      <c r="AD8" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="AE8" s="16" t="s">
+      <c r="AE8" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="AF8" s="16"/>
-      <c r="AG8" s="16"/>
-      <c r="AH8" s="18" t="s">
+      <c r="AF8" s="17"/>
+      <c r="AG8" s="17"/>
+      <c r="AH8" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="AI8" s="26" t="s">
-        <v>240</v>
-      </c>
-      <c r="AJ8" s="18" t="s">
+      <c r="AI8" s="27" t="s">
+        <v>265</v>
+      </c>
+      <c r="AJ8" s="19" t="s">
         <v>65</v>
       </c>
-      <c r="AK8" s="18" t="s">
-        <v>241</v>
-      </c>
-      <c r="AL8" s="18"/>
-      <c r="AM8" s="18"/>
-      <c r="AN8" s="19" t="s">
-        <v>242</v>
+      <c r="AK8" s="19" t="s">
+        <v>266</v>
+      </c>
+      <c r="AL8" s="19"/>
+      <c r="AM8" s="19"/>
+      <c r="AN8" s="20" t="s">
+        <v>267</v>
       </c>
       <c r="AO8" s="1"/>
       <c r="AP8" s="1"/>
@@ -5283,15 +5398,15 @@
       <c r="AR8" s="1"/>
       <c r="AS8" s="1"/>
       <c r="AT8" s="1"/>
-      <c r="AU8" s="20" t="s">
-        <v>142</v>
+      <c r="AU8" s="21" t="s">
+        <v>268</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="B10" s="21" t="s">
+        <v>269</v>
+      </c>
+      <c r="B10" s="22" t="s">
         <v>41</v>
       </c>
       <c r="C10" s="1" t="s">
@@ -5300,21 +5415,21 @@
       <c r="D10" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="E10" s="21" t="s">
-        <v>244</v>
+      <c r="E10" s="22" t="s">
+        <v>270</v>
       </c>
       <c r="F10" s="11" t="n">
         <v>46027</v>
       </c>
       <c r="G10" s="1"/>
       <c r="H10" s="1"/>
-      <c r="I10" s="12" t="s">
+      <c r="I10" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="J10" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="K10" s="12" t="s">
+      <c r="J10" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="K10" s="13" t="s">
         <v>46</v>
       </c>
       <c r="L10" s="1"/>
@@ -5322,7 +5437,7 @@
       <c r="N10" s="1"/>
       <c r="O10" s="1"/>
       <c r="P10" s="1" t="s">
-        <v>245</v>
+        <v>271</v>
       </c>
       <c r="Q10" s="8"/>
       <c r="R10" s="8"/>
@@ -5330,41 +5445,41 @@
       <c r="T10" s="8"/>
       <c r="U10" s="8"/>
       <c r="V10" s="8"/>
-      <c r="W10" s="14" t="s">
+      <c r="W10" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="X10" s="14"/>
-      <c r="Y10" s="14" t="s">
+      <c r="X10" s="15"/>
+      <c r="Y10" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="Z10" s="14"/>
-      <c r="AA10" s="14"/>
-      <c r="AB10" s="14"/>
-      <c r="AC10" s="14"/>
-      <c r="AD10" s="16" t="s">
+      <c r="Z10" s="15"/>
+      <c r="AA10" s="15"/>
+      <c r="AB10" s="15"/>
+      <c r="AC10" s="15"/>
+      <c r="AD10" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="AE10" s="16" t="s">
+      <c r="AE10" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="AF10" s="16"/>
-      <c r="AG10" s="16"/>
-      <c r="AH10" s="18" t="s">
-        <v>246</v>
-      </c>
-      <c r="AI10" s="18" t="s">
-        <v>247</v>
-      </c>
-      <c r="AJ10" s="18" t="s">
+      <c r="AF10" s="17"/>
+      <c r="AG10" s="17"/>
+      <c r="AH10" s="19" t="s">
+        <v>272</v>
+      </c>
+      <c r="AI10" s="19" t="s">
+        <v>273</v>
+      </c>
+      <c r="AJ10" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="AK10" s="18" t="s">
+      <c r="AK10" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="AL10" s="18"/>
-      <c r="AM10" s="18"/>
-      <c r="AN10" s="19" t="s">
-        <v>248</v>
+      <c r="AL10" s="19"/>
+      <c r="AM10" s="19"/>
+      <c r="AN10" s="20" t="s">
+        <v>274</v>
       </c>
       <c r="AO10" s="1"/>
       <c r="AP10" s="1"/>
@@ -5372,15 +5487,15 @@
       <c r="AR10" s="1"/>
       <c r="AS10" s="1"/>
       <c r="AT10" s="1"/>
-      <c r="AU10" s="20" t="s">
-        <v>249</v>
+      <c r="AU10" s="21" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="B12" s="21" t="s">
+        <v>276</v>
+      </c>
+      <c r="B12" s="22" t="s">
         <v>41</v>
       </c>
       <c r="C12" s="1" t="s">
@@ -5390,20 +5505,20 @@
         <v>43</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="F12" s="22" t="n">
+        <v>193</v>
+      </c>
+      <c r="F12" s="23" t="n">
         <v>46027</v>
       </c>
       <c r="G12" s="1"/>
       <c r="H12" s="1"/>
-      <c r="I12" s="12" t="s">
+      <c r="I12" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="J12" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="K12" s="12" t="s">
+      <c r="J12" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="K12" s="13" t="s">
         <v>46</v>
       </c>
       <c r="L12" s="1"/>
@@ -5411,7 +5526,7 @@
       <c r="N12" s="1"/>
       <c r="O12" s="1"/>
       <c r="P12" s="1" t="s">
-        <v>251</v>
+        <v>277</v>
       </c>
       <c r="Q12" s="8"/>
       <c r="R12" s="8"/>
@@ -5419,41 +5534,41 @@
       <c r="T12" s="8"/>
       <c r="U12" s="8"/>
       <c r="V12" s="8"/>
-      <c r="W12" s="14" t="s">
+      <c r="W12" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="X12" s="14"/>
-      <c r="Y12" s="14" t="s">
+      <c r="X12" s="15"/>
+      <c r="Y12" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="Z12" s="14"/>
-      <c r="AA12" s="14"/>
-      <c r="AB12" s="14"/>
-      <c r="AC12" s="14"/>
-      <c r="AD12" s="16" t="s">
+      <c r="Z12" s="15"/>
+      <c r="AA12" s="15"/>
+      <c r="AB12" s="15"/>
+      <c r="AC12" s="15"/>
+      <c r="AD12" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="AE12" s="16" t="s">
+      <c r="AE12" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="AF12" s="16"/>
-      <c r="AG12" s="16"/>
-      <c r="AH12" s="18" t="s">
-        <v>91</v>
-      </c>
-      <c r="AI12" s="18" t="s">
-        <v>247</v>
-      </c>
-      <c r="AJ12" s="18" t="s">
+      <c r="AF12" s="17"/>
+      <c r="AG12" s="17"/>
+      <c r="AH12" s="19" t="s">
+        <v>95</v>
+      </c>
+      <c r="AI12" s="19" t="s">
+        <v>273</v>
+      </c>
+      <c r="AJ12" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="AK12" s="18" t="s">
+      <c r="AK12" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="AL12" s="18"/>
-      <c r="AM12" s="18"/>
-      <c r="AN12" s="19" t="s">
-        <v>252</v>
+      <c r="AL12" s="19"/>
+      <c r="AM12" s="19"/>
+      <c r="AN12" s="20" t="s">
+        <v>278</v>
       </c>
       <c r="AO12" s="1"/>
       <c r="AP12" s="1"/>
@@ -5461,15 +5576,15 @@
       <c r="AR12" s="1"/>
       <c r="AS12" s="1"/>
       <c r="AT12" s="1"/>
-      <c r="AU12" s="20" t="s">
-        <v>244</v>
+      <c r="AU12" s="21" t="s">
+        <v>270</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="B14" s="21" t="s">
+        <v>279</v>
+      </c>
+      <c r="B14" s="22" t="s">
         <v>41</v>
       </c>
       <c r="C14" s="1" t="s">
@@ -5478,21 +5593,21 @@
       <c r="D14" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="E14" s="21" t="s">
-        <v>210</v>
+      <c r="E14" s="22" t="s">
+        <v>232</v>
       </c>
       <c r="F14" s="11" t="n">
         <v>46027</v>
       </c>
       <c r="G14" s="1"/>
       <c r="H14" s="1"/>
-      <c r="I14" s="12" t="s">
+      <c r="I14" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="J14" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="K14" s="12" t="s">
+      <c r="J14" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="K14" s="13" t="s">
         <v>46</v>
       </c>
       <c r="L14" s="1"/>
@@ -5500,7 +5615,7 @@
       <c r="N14" s="1"/>
       <c r="O14" s="1"/>
       <c r="P14" s="1" t="s">
-        <v>254</v>
+        <v>280</v>
       </c>
       <c r="Q14" s="8"/>
       <c r="R14" s="8"/>
@@ -5508,41 +5623,41 @@
       <c r="T14" s="8"/>
       <c r="U14" s="8"/>
       <c r="V14" s="8"/>
-      <c r="W14" s="14" t="s">
+      <c r="W14" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="X14" s="14"/>
-      <c r="Y14" s="14" t="s">
+      <c r="X14" s="15"/>
+      <c r="Y14" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="Z14" s="14"/>
-      <c r="AA14" s="14"/>
-      <c r="AB14" s="14"/>
-      <c r="AC14" s="14"/>
-      <c r="AD14" s="16" t="s">
+      <c r="Z14" s="15"/>
+      <c r="AA14" s="15"/>
+      <c r="AB14" s="15"/>
+      <c r="AC14" s="15"/>
+      <c r="AD14" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="AE14" s="16" t="s">
+      <c r="AE14" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="AF14" s="16"/>
-      <c r="AG14" s="16"/>
-      <c r="AH14" s="18" t="s">
+      <c r="AF14" s="17"/>
+      <c r="AG14" s="17"/>
+      <c r="AH14" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="AI14" s="18" t="s">
+      <c r="AI14" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="AJ14" s="18" t="s">
+      <c r="AJ14" s="19" t="s">
         <v>65</v>
       </c>
-      <c r="AK14" s="18" t="s">
+      <c r="AK14" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="AL14" s="18"/>
-      <c r="AM14" s="18"/>
-      <c r="AN14" s="19" t="s">
-        <v>255</v>
+      <c r="AL14" s="19"/>
+      <c r="AM14" s="19"/>
+      <c r="AN14" s="20" t="s">
+        <v>281</v>
       </c>
       <c r="AO14" s="1"/>
       <c r="AP14" s="1"/>
@@ -5550,8 +5665,8 @@
       <c r="AR14" s="1"/>
       <c r="AS14" s="1"/>
       <c r="AT14" s="1"/>
-      <c r="AU14" s="20" t="s">
-        <v>185</v>
+      <c r="AU14" s="21" t="s">
+        <v>282</v>
       </c>
     </row>
   </sheetData>
